--- a/data/ISQ Pipeline 2026.xlsx
+++ b/data/ISQ Pipeline 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10712"/>
   <workbookPr updateLinks="always" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl.sharepoint.com/sites/ISQPMO/Finances/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinfojtek/__AI_Coding/_DHL/05_Project_Pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7127" documentId="13_ncr:1_{8DE09539-96E4-41E5-BCC6-211D8B3849B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF714669-C718-43BC-9EBA-AC7200C0A6CF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA50951E-2F8F-5947-BAF2-533AE03BB2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10650" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2FE2297C-0A07-4B33-BC0D-8A32EA6787F9}"/>
+    <workbookView xWindow="13400" yWindow="6560" windowWidth="30240" windowHeight="19640" xr2:uid="{2FE2297C-0A07-4B33-BC0D-8A32EA6787F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Project List 2026" sheetId="7" r:id="rId1"/>
@@ -28,8 +28,8 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId8"/>
-    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="11" r:id="rId8"/>
+    <pivotCache cacheId="12" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -3148,7 +3148,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3501,23 +3501,14 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3526,79 +3517,6 @@
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="190">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFA3A3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -5805,6 +5723,79 @@
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFA3A3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -7729,10 +7720,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Sandra Harris (DHL IT Services)" id="{901F0CD4-9A00-475B-A0BB-A1215526915A}" userId="S::sandra.harris@dhl.com::7a86718c-3daa-44f4-b19a-9b64060cec39" providerId="AD"/>
@@ -14343,7 +14330,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{61836ECD-07B7-43F8-BA55-C16C977AFED1}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="PM">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{61836ECD-07B7-43F8-BA55-C16C977AFED1}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="PM">
   <location ref="A7:M20" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="5" colPageCount="1"/>
   <pivotFields count="25">
     <pivotField axis="axisPage" showAll="0">
@@ -14673,13 +14660,13 @@
     <dataField name="12/2026" fld="23" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="189">
+    <format dxfId="179">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="188">
+    <format dxfId="178">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="187">
+    <format dxfId="177">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="11">
@@ -14698,26 +14685,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="186">
+    <format dxfId="176">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="185">
+    <format dxfId="175">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="184">
+    <format dxfId="174">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="183">
+    <format dxfId="173">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="182">
+    <format dxfId="172">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="181">
+    <format dxfId="171">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="11">
@@ -14738,7 +14725,294 @@
     </format>
   </formats>
   <conditionalFormats count="10">
-    <conditionalFormat priority="1">
+    <conditionalFormat priority="10">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4" count="31">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+              <x v="12"/>
+              <x v="13"/>
+              <x v="14"/>
+              <x v="15"/>
+              <x v="16"/>
+              <x v="17"/>
+              <x v="18"/>
+              <x v="19"/>
+              <x v="20"/>
+              <x v="21"/>
+              <x v="22"/>
+              <x v="23"/>
+              <x v="24"/>
+              <x v="25"/>
+              <x v="26"/>
+              <x v="27"/>
+              <x v="28"/>
+              <x v="29"/>
+              <x v="30"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="9">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4" count="31">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+              <x v="12"/>
+              <x v="13"/>
+              <x v="14"/>
+              <x v="15"/>
+              <x v="16"/>
+              <x v="17"/>
+              <x v="18"/>
+              <x v="19"/>
+              <x v="20"/>
+              <x v="21"/>
+              <x v="22"/>
+              <x v="23"/>
+              <x v="24"/>
+              <x v="25"/>
+              <x v="26"/>
+              <x v="27"/>
+              <x v="28"/>
+              <x v="29"/>
+              <x v="30"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="8">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4" count="31">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+              <x v="12"/>
+              <x v="13"/>
+              <x v="14"/>
+              <x v="15"/>
+              <x v="16"/>
+              <x v="17"/>
+              <x v="18"/>
+              <x v="19"/>
+              <x v="20"/>
+              <x v="21"/>
+              <x v="22"/>
+              <x v="23"/>
+              <x v="24"/>
+              <x v="25"/>
+              <x v="26"/>
+              <x v="27"/>
+              <x v="28"/>
+              <x v="29"/>
+              <x v="30"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="7">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4" count="31">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+              <x v="12"/>
+              <x v="13"/>
+              <x v="14"/>
+              <x v="15"/>
+              <x v="16"/>
+              <x v="17"/>
+              <x v="18"/>
+              <x v="19"/>
+              <x v="20"/>
+              <x v="21"/>
+              <x v="22"/>
+              <x v="23"/>
+              <x v="24"/>
+              <x v="25"/>
+              <x v="26"/>
+              <x v="27"/>
+              <x v="28"/>
+              <x v="29"/>
+              <x v="30"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="6">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4" count="31">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+              <x v="12"/>
+              <x v="13"/>
+              <x v="14"/>
+              <x v="15"/>
+              <x v="16"/>
+              <x v="17"/>
+              <x v="18"/>
+              <x v="19"/>
+              <x v="20"/>
+              <x v="21"/>
+              <x v="22"/>
+              <x v="23"/>
+              <x v="24"/>
+              <x v="25"/>
+              <x v="26"/>
+              <x v="27"/>
+              <x v="28"/>
+              <x v="29"/>
+              <x v="30"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="5">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4" count="31">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+              <x v="12"/>
+              <x v="13"/>
+              <x v="14"/>
+              <x v="15"/>
+              <x v="16"/>
+              <x v="17"/>
+              <x v="18"/>
+              <x v="19"/>
+              <x v="20"/>
+              <x v="21"/>
+              <x v="22"/>
+              <x v="23"/>
+              <x v="24"/>
+              <x v="25"/>
+              <x v="26"/>
+              <x v="27"/>
+              <x v="28"/>
+              <x v="29"/>
+              <x v="30"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="4">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4" count="31">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+              <x v="12"/>
+              <x v="13"/>
+              <x v="14"/>
+              <x v="15"/>
+              <x v="16"/>
+              <x v="17"/>
+              <x v="18"/>
+              <x v="19"/>
+              <x v="20"/>
+              <x v="21"/>
+              <x v="22"/>
+              <x v="23"/>
+              <x v="24"/>
+              <x v="25"/>
+              <x v="26"/>
+              <x v="27"/>
+              <x v="28"/>
+              <x v="29"/>
+              <x v="30"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="3">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="1">
@@ -14820,294 +15094,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="3">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="1">
-            <reference field="4" count="31">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-              <x v="12"/>
-              <x v="13"/>
-              <x v="14"/>
-              <x v="15"/>
-              <x v="16"/>
-              <x v="17"/>
-              <x v="18"/>
-              <x v="19"/>
-              <x v="20"/>
-              <x v="21"/>
-              <x v="22"/>
-              <x v="23"/>
-              <x v="24"/>
-              <x v="25"/>
-              <x v="26"/>
-              <x v="27"/>
-              <x v="28"/>
-              <x v="29"/>
-              <x v="30"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="4">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="1">
-            <reference field="4" count="31">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-              <x v="12"/>
-              <x v="13"/>
-              <x v="14"/>
-              <x v="15"/>
-              <x v="16"/>
-              <x v="17"/>
-              <x v="18"/>
-              <x v="19"/>
-              <x v="20"/>
-              <x v="21"/>
-              <x v="22"/>
-              <x v="23"/>
-              <x v="24"/>
-              <x v="25"/>
-              <x v="26"/>
-              <x v="27"/>
-              <x v="28"/>
-              <x v="29"/>
-              <x v="30"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="5">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="1">
-            <reference field="4" count="31">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-              <x v="12"/>
-              <x v="13"/>
-              <x v="14"/>
-              <x v="15"/>
-              <x v="16"/>
-              <x v="17"/>
-              <x v="18"/>
-              <x v="19"/>
-              <x v="20"/>
-              <x v="21"/>
-              <x v="22"/>
-              <x v="23"/>
-              <x v="24"/>
-              <x v="25"/>
-              <x v="26"/>
-              <x v="27"/>
-              <x v="28"/>
-              <x v="29"/>
-              <x v="30"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="6">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="1">
-            <reference field="4" count="31">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-              <x v="12"/>
-              <x v="13"/>
-              <x v="14"/>
-              <x v="15"/>
-              <x v="16"/>
-              <x v="17"/>
-              <x v="18"/>
-              <x v="19"/>
-              <x v="20"/>
-              <x v="21"/>
-              <x v="22"/>
-              <x v="23"/>
-              <x v="24"/>
-              <x v="25"/>
-              <x v="26"/>
-              <x v="27"/>
-              <x v="28"/>
-              <x v="29"/>
-              <x v="30"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="7">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="1">
-            <reference field="4" count="31">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-              <x v="12"/>
-              <x v="13"/>
-              <x v="14"/>
-              <x v="15"/>
-              <x v="16"/>
-              <x v="17"/>
-              <x v="18"/>
-              <x v="19"/>
-              <x v="20"/>
-              <x v="21"/>
-              <x v="22"/>
-              <x v="23"/>
-              <x v="24"/>
-              <x v="25"/>
-              <x v="26"/>
-              <x v="27"/>
-              <x v="28"/>
-              <x v="29"/>
-              <x v="30"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="8">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="1">
-            <reference field="4" count="31">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-              <x v="12"/>
-              <x v="13"/>
-              <x v="14"/>
-              <x v="15"/>
-              <x v="16"/>
-              <x v="17"/>
-              <x v="18"/>
-              <x v="19"/>
-              <x v="20"/>
-              <x v="21"/>
-              <x v="22"/>
-              <x v="23"/>
-              <x v="24"/>
-              <x v="25"/>
-              <x v="26"/>
-              <x v="27"/>
-              <x v="28"/>
-              <x v="29"/>
-              <x v="30"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="9">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="1">
-            <reference field="4" count="31">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-              <x v="12"/>
-              <x v="13"/>
-              <x v="14"/>
-              <x v="15"/>
-              <x v="16"/>
-              <x v="17"/>
-              <x v="18"/>
-              <x v="19"/>
-              <x v="20"/>
-              <x v="21"/>
-              <x v="22"/>
-              <x v="23"/>
-              <x v="24"/>
-              <x v="25"/>
-              <x v="26"/>
-              <x v="27"/>
-              <x v="28"/>
-              <x v="29"/>
-              <x v="30"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="10">
+    <conditionalFormat priority="1">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="1">
@@ -15162,7 +15149,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6805432F-4BE8-4CCF-BB12-7A9D94EE41DF}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6805432F-4BE8-4CCF-BB12-7A9D94EE41DF}" name="PivotTable2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="24">
     <pivotField dataField="1" showAll="0"/>
@@ -15258,7 +15245,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{07E0516F-53AE-4F0D-949C-97573579D569}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{07E0516F-53AE-4F0D-949C-97573579D569}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="16">
   <location ref="A38:B46" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="24">
     <pivotField dataField="1" showAll="0"/>
@@ -15393,7 +15380,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F3E4F6D-71E0-4C17-B7CC-5EF155C14674}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F3E4F6D-71E0-4C17-B7CC-5EF155C14674}" name="PivotTable3" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A21:B26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="24">
     <pivotField dataField="1" showAll="0"/>
@@ -15896,29 +15883,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A235DE4-D972-468C-8B47-B4E3BC626216}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:P205"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40.453125" customWidth="1"/>
-    <col min="2" max="2" width="43.453125" customWidth="1"/>
-    <col min="3" max="4" width="16.81640625" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" style="40" customWidth="1"/>
-    <col min="7" max="7" width="18.54296875" style="40" customWidth="1"/>
-    <col min="8" max="8" width="22.54296875" customWidth="1"/>
-    <col min="9" max="9" width="11.54296875" customWidth="1"/>
-    <col min="10" max="11" width="13.54296875" style="40" customWidth="1"/>
-    <col min="12" max="12" width="9.1796875" style="40"/>
-    <col min="13" max="13" width="15.54296875" customWidth="1"/>
-    <col min="14" max="14" width="10.54296875" customWidth="1"/>
-    <col min="15" max="15" width="15.54296875" customWidth="1"/>
-    <col min="16" max="16" width="59.453125" customWidth="1"/>
+    <col min="1" max="1" width="40.5" customWidth="1"/>
+    <col min="2" max="2" width="43.5" customWidth="1"/>
+    <col min="3" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="40" customWidth="1"/>
+    <col min="7" max="7" width="18.5" style="40" customWidth="1"/>
+    <col min="8" max="8" width="22.5" customWidth="1"/>
+    <col min="9" max="9" width="11.5" customWidth="1"/>
+    <col min="10" max="11" width="13.5" style="40" customWidth="1"/>
+    <col min="12" max="12" width="9.1640625" style="40"/>
+    <col min="13" max="13" width="15.5" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="15" width="15.5" customWidth="1"/>
+    <col min="16" max="16" width="59.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="57.65" customHeight="1">
+    <row r="1" spans="1:16" ht="57.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -15968,7 +15955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1">
+    <row r="2" spans="1:16">
       <c r="A2" s="7" t="s">
         <v>16</v>
       </c>
@@ -16019,7 +16006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1">
+    <row r="3" spans="1:16">
       <c r="A3" s="7" t="s">
         <v>26</v>
       </c>
@@ -16070,7 +16057,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:16" hidden="1">
+    <row r="4" spans="1:16">
       <c r="A4" s="7" t="s">
         <v>30</v>
       </c>
@@ -16121,7 +16108,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1">
+    <row r="5" spans="1:16">
       <c r="A5" s="7" t="s">
         <v>33</v>
       </c>
@@ -16172,7 +16159,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:16" hidden="1">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -16223,7 +16210,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:16" hidden="1">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -16271,7 +16258,7 @@
         <v>294645</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1">
+    <row r="8" spans="1:16">
       <c r="A8" s="15" t="s">
         <v>44</v>
       </c>
@@ -16322,7 +16309,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -16373,7 +16360,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1">
+    <row r="10" spans="1:16">
       <c r="A10" s="7" t="s">
         <v>50</v>
       </c>
@@ -16421,7 +16408,7 @@
         <v>37236.639999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1">
+    <row r="11" spans="1:16" ht="16">
       <c r="A11" s="45" t="s">
         <v>57</v>
       </c>
@@ -16472,7 +16459,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1">
+    <row r="12" spans="1:16">
       <c r="A12" s="7" t="s">
         <v>62</v>
       </c>
@@ -16523,7 +16510,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1">
+    <row r="13" spans="1:16">
       <c r="A13" s="7" t="s">
         <v>65</v>
       </c>
@@ -16571,7 +16558,7 @@
         <v>34225.230000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1">
+    <row r="14" spans="1:16">
       <c r="A14" s="7" t="s">
         <v>67</v>
       </c>
@@ -16619,7 +16606,7 @@
         <v>13344.31</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1">
+    <row r="15" spans="1:16">
       <c r="A15" s="7" t="s">
         <v>70</v>
       </c>
@@ -16668,7 +16655,7 @@
       </c>
       <c r="P15" s="7"/>
     </row>
-    <row r="16" spans="1:16" hidden="1">
+    <row r="16" spans="1:16">
       <c r="A16" s="7" t="s">
         <v>72</v>
       </c>
@@ -16717,7 +16704,7 @@
       </c>
       <c r="P16" s="7"/>
     </row>
-    <row r="17" spans="1:16" hidden="1">
+    <row r="17" spans="1:16">
       <c r="A17" s="45" t="s">
         <v>57</v>
       </c>
@@ -16768,7 +16755,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1">
+    <row r="18" spans="1:16">
       <c r="A18" s="7" t="s">
         <v>76</v>
       </c>
@@ -16816,7 +16803,7 @@
       </c>
       <c r="P18" s="7"/>
     </row>
-    <row r="19" spans="1:16" hidden="1">
+    <row r="19" spans="1:16">
       <c r="A19" s="7" t="s">
         <v>80</v>
       </c>
@@ -16867,7 +16854,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1">
+    <row r="20" spans="1:16">
       <c r="A20" s="7" t="s">
         <v>82</v>
       </c>
@@ -16915,7 +16902,7 @@
         <v>6817.92</v>
       </c>
     </row>
-    <row r="21" spans="1:16" hidden="1">
+    <row r="21" spans="1:16">
       <c r="A21" s="7" t="s">
         <v>85</v>
       </c>
@@ -16963,7 +16950,7 @@
         <v>4849.6000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:16" hidden="1">
+    <row r="22" spans="1:16">
       <c r="A22" s="7" t="s">
         <v>87</v>
       </c>
@@ -17011,7 +16998,7 @@
         <v>4849.6000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:16" hidden="1">
+    <row r="23" spans="1:16">
       <c r="A23" s="7" t="s">
         <v>89</v>
       </c>
@@ -17059,7 +17046,7 @@
         <v>9699.2000000000007</v>
       </c>
     </row>
-    <row r="24" spans="1:16" hidden="1">
+    <row r="24" spans="1:16">
       <c r="A24" s="7" t="s">
         <v>91</v>
       </c>
@@ -17107,7 +17094,7 @@
         <v>14548.8</v>
       </c>
     </row>
-    <row r="25" spans="1:16" hidden="1">
+    <row r="25" spans="1:16">
       <c r="A25" s="7" t="s">
         <v>93</v>
       </c>
@@ -17155,7 +17142,7 @@
         <v>9699.2000000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:16" hidden="1">
+    <row r="26" spans="1:16">
       <c r="A26" s="7" t="s">
         <v>95</v>
       </c>
@@ -17203,7 +17190,7 @@
         <v>29097.599999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1">
+    <row r="27" spans="1:16">
       <c r="A27" s="7" t="s">
         <v>97</v>
       </c>
@@ -17251,7 +17238,7 @@
         <v>16517.12</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1">
+    <row r="28" spans="1:16">
       <c r="A28" s="7" t="s">
         <v>99</v>
       </c>
@@ -17299,7 +17286,7 @@
         <v>4849.6000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1">
+    <row r="29" spans="1:16">
       <c r="A29" s="7" t="s">
         <v>101</v>
       </c>
@@ -17347,7 +17334,7 @@
         <v>9699.2000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:16" hidden="1">
+    <row r="30" spans="1:16">
       <c r="A30" s="7" t="s">
         <v>103</v>
       </c>
@@ -17395,7 +17382,7 @@
         <v>9699.2000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:16" hidden="1">
+    <row r="31" spans="1:16">
       <c r="A31" s="7" t="s">
         <v>105</v>
       </c>
@@ -17443,7 +17430,7 @@
         <v>9699.2000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:16" hidden="1">
+    <row r="32" spans="1:16">
       <c r="A32" s="7" t="s">
         <v>107</v>
       </c>
@@ -17491,7 +17478,7 @@
         <v>22350.880000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1">
+    <row r="33" spans="1:16">
       <c r="A33" s="7" t="s">
         <v>109</v>
       </c>
@@ -17539,7 +17526,7 @@
         <v>4849.6000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1">
+    <row r="34" spans="1:16">
       <c r="A34" s="7" t="s">
         <v>111</v>
       </c>
@@ -17587,7 +17574,7 @@
         <v>23335.040000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1">
+    <row r="35" spans="1:16">
       <c r="A35" s="7" t="s">
         <v>113</v>
       </c>
@@ -17635,7 +17622,7 @@
         <v>19398.400000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1">
+    <row r="36" spans="1:16" ht="16">
       <c r="A36" s="45" t="s">
         <v>115</v>
       </c>
@@ -17683,7 +17670,7 @@
         <v>5239.4399999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1">
+    <row r="37" spans="1:16">
       <c r="A37" s="7" t="s">
         <v>118</v>
       </c>
@@ -17734,7 +17721,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:16" hidden="1">
+    <row r="38" spans="1:16">
       <c r="A38" s="7" t="s">
         <v>122</v>
       </c>
@@ -17785,7 +17772,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1">
+    <row r="39" spans="1:16">
       <c r="A39" s="7" t="s">
         <v>125</v>
       </c>
@@ -17833,7 +17820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1">
+    <row r="40" spans="1:16">
       <c r="A40" s="7" t="s">
         <v>128</v>
       </c>
@@ -17881,7 +17868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1">
+    <row r="41" spans="1:16">
       <c r="A41" s="7" t="s">
         <v>131</v>
       </c>
@@ -17929,7 +17916,7 @@
         <v>1858.4</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1">
+    <row r="42" spans="1:16">
       <c r="A42" s="7" t="s">
         <v>134</v>
       </c>
@@ -17977,7 +17964,7 @@
         <v>1858.4</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1">
+    <row r="43" spans="1:16">
       <c r="A43" s="7" t="s">
         <v>136</v>
       </c>
@@ -18025,7 +18012,7 @@
         <v>1858.4</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1">
+    <row r="44" spans="1:16">
       <c r="A44" s="7" t="s">
         <v>138</v>
       </c>
@@ -18073,7 +18060,7 @@
         <v>1858.4</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1">
+    <row r="45" spans="1:16">
       <c r="A45" s="7" t="s">
         <v>140</v>
       </c>
@@ -18121,7 +18108,7 @@
         <v>1858.4</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1">
+    <row r="46" spans="1:16">
       <c r="A46" s="7" t="s">
         <v>142</v>
       </c>
@@ -18169,7 +18156,7 @@
         <v>1858.4</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1">
+    <row r="47" spans="1:16">
       <c r="A47" s="7" t="s">
         <v>144</v>
       </c>
@@ -18217,7 +18204,7 @@
         <v>1858.4</v>
       </c>
     </row>
-    <row r="48" spans="1:16" hidden="1">
+    <row r="48" spans="1:16">
       <c r="A48" s="7" t="s">
         <v>146</v>
       </c>
@@ -18265,7 +18252,7 @@
         <v>1858.4</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1">
+    <row r="49" spans="1:16" ht="16">
       <c r="A49" s="45" t="s">
         <v>148</v>
       </c>
@@ -18316,7 +18303,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1">
+    <row r="50" spans="1:16">
       <c r="A50" s="7" t="s">
         <v>153</v>
       </c>
@@ -18365,7 +18352,7 @@
       </c>
       <c r="P50" s="7"/>
     </row>
-    <row r="51" spans="1:16" hidden="1">
+    <row r="51" spans="1:16">
       <c r="A51" s="7" t="s">
         <v>156</v>
       </c>
@@ -18414,7 +18401,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1">
+    <row r="52" spans="1:16">
       <c r="A52" s="7" t="s">
         <v>159</v>
       </c>
@@ -18463,7 +18450,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="53" spans="1:16" hidden="1">
+    <row r="53" spans="1:16">
       <c r="A53" t="s">
         <v>161</v>
       </c>
@@ -18514,7 +18501,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="54" spans="1:16" hidden="1">
+    <row r="54" spans="1:16">
       <c r="A54" t="s">
         <v>166</v>
       </c>
@@ -18562,7 +18549,7 @@
         <v>4453</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1">
+    <row r="55" spans="1:16">
       <c r="A55" t="s">
         <v>168</v>
       </c>
@@ -18814,7 +18801,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1">
+    <row r="60" spans="1:16">
       <c r="A60" s="7" t="s">
         <v>180</v>
       </c>
@@ -18846,7 +18833,7 @@
         <v>45777</v>
       </c>
       <c r="K60" s="42">
-        <v>46112</v>
+        <v>46477</v>
       </c>
       <c r="L60" s="35" t="s">
         <v>39</v>
@@ -18862,7 +18849,7 @@
         <v>14325</v>
       </c>
     </row>
-    <row r="61" spans="1:16" hidden="1">
+    <row r="61" spans="1:16">
       <c r="A61" s="7" t="s">
         <v>184</v>
       </c>
@@ -18910,7 +18897,7 @@
         <v>1863.54</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1">
+    <row r="62" spans="1:16">
       <c r="A62" s="7" t="s">
         <v>186</v>
       </c>
@@ -18958,7 +18945,7 @@
         <v>8195</v>
       </c>
     </row>
-    <row r="63" spans="1:16" hidden="1">
+    <row r="63" spans="1:16" ht="16">
       <c r="A63" s="7" t="s">
         <v>188</v>
       </c>
@@ -19006,7 +18993,7 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1">
+    <row r="64" spans="1:16">
       <c r="A64" s="7" t="s">
         <v>192</v>
       </c>
@@ -19054,7 +19041,7 @@
         <v>4172</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1">
+    <row r="65" spans="1:16">
       <c r="A65" t="s">
         <v>195</v>
       </c>
@@ -19102,7 +19089,7 @@
         <v>24830</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1">
+    <row r="66" spans="1:16">
       <c r="A66" t="s">
         <v>197</v>
       </c>
@@ -19153,7 +19140,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1">
+    <row r="67" spans="1:16">
       <c r="A67" s="32" t="s">
         <v>200</v>
       </c>
@@ -19185,7 +19172,7 @@
         <v>45931</v>
       </c>
       <c r="K67" s="37">
-        <v>46053</v>
+        <v>46418</v>
       </c>
       <c r="L67" s="35" t="s">
         <v>39</v>
@@ -19201,7 +19188,7 @@
         <v>28932.32</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1">
+    <row r="68" spans="1:16" ht="16">
       <c r="A68" t="s">
         <v>203</v>
       </c>
@@ -19249,7 +19236,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1">
+    <row r="69" spans="1:16">
       <c r="A69" t="s">
         <v>204</v>
       </c>
@@ -19300,7 +19287,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1">
+    <row r="70" spans="1:16">
       <c r="A70" s="7" t="s">
         <v>207</v>
       </c>
@@ -19348,7 +19335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1">
+    <row r="71" spans="1:16">
       <c r="A71" s="7" t="s">
         <v>209</v>
       </c>
@@ -19396,7 +19383,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1">
+    <row r="72" spans="1:16">
       <c r="A72" t="s">
         <v>211</v>
       </c>
@@ -19445,7 +19432,7 @@
       </c>
       <c r="P72" s="21"/>
     </row>
-    <row r="73" spans="1:16" hidden="1">
+    <row r="73" spans="1:16">
       <c r="A73" t="s">
         <v>214</v>
       </c>
@@ -19493,7 +19480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1">
+    <row r="74" spans="1:16">
       <c r="A74" t="s">
         <v>215</v>
       </c>
@@ -19544,7 +19531,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1">
+    <row r="75" spans="1:16">
       <c r="A75" t="s">
         <v>219</v>
       </c>
@@ -19574,7 +19561,7 @@
         <v>46054</v>
       </c>
       <c r="K75" s="42">
-        <v>46295</v>
+        <v>46660</v>
       </c>
       <c r="L75" s="35" t="s">
         <v>24</v>
@@ -19593,7 +19580,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1">
+    <row r="76" spans="1:16">
       <c r="A76" s="7" t="s">
         <v>221</v>
       </c>
@@ -19642,7 +19629,7 @@
       </c>
       <c r="P76" s="7"/>
     </row>
-    <row r="77" spans="1:16" hidden="1">
+    <row r="77" spans="1:16">
       <c r="A77" s="7" t="s">
         <v>225</v>
       </c>
@@ -19693,7 +19680,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1">
+    <row r="78" spans="1:16">
       <c r="A78" s="7" t="s">
         <v>228</v>
       </c>
@@ -19742,7 +19729,7 @@
       </c>
       <c r="P78" s="7"/>
     </row>
-    <row r="79" spans="1:16" hidden="1">
+    <row r="79" spans="1:16">
       <c r="A79" s="7" t="s">
         <v>232</v>
       </c>
@@ -19791,7 +19778,7 @@
       </c>
       <c r="P79" s="7"/>
     </row>
-    <row r="80" spans="1:16" hidden="1">
+    <row r="80" spans="1:16" ht="16">
       <c r="A80" s="7" t="s">
         <v>234</v>
       </c>
@@ -19842,7 +19829,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="81" spans="1:16" hidden="1">
+    <row r="81" spans="1:16">
       <c r="A81" t="s">
         <v>239</v>
       </c>
@@ -19890,7 +19877,7 @@
         <v>9008.16</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1">
+    <row r="82" spans="1:16">
       <c r="A82" s="7" t="s">
         <v>241</v>
       </c>
@@ -19941,7 +19928,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1">
+    <row r="83" spans="1:16">
       <c r="A83" s="7" t="s">
         <v>244</v>
       </c>
@@ -19989,7 +19976,7 @@
         <v>474281</v>
       </c>
     </row>
-    <row r="84" spans="1:16" hidden="1">
+    <row r="84" spans="1:16">
       <c r="A84" s="7" t="s">
         <v>248</v>
       </c>
@@ -20040,7 +20027,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1">
+    <row r="85" spans="1:16">
       <c r="A85" s="7" t="s">
         <v>252</v>
       </c>
@@ -20091,7 +20078,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1">
+    <row r="86" spans="1:16">
       <c r="A86" s="7" t="s">
         <v>253</v>
       </c>
@@ -20142,7 +20129,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1">
+    <row r="87" spans="1:16">
       <c r="A87" s="7" t="s">
         <v>254</v>
       </c>
@@ -20174,7 +20161,7 @@
         <v>46023</v>
       </c>
       <c r="K87" s="37">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="L87" s="35" t="s">
         <v>35</v>
@@ -20193,7 +20180,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1">
+    <row r="88" spans="1:16">
       <c r="A88" s="7" t="s">
         <v>257</v>
       </c>
@@ -20242,7 +20229,7 @@
       </c>
       <c r="P88" s="7"/>
     </row>
-    <row r="89" spans="1:16" hidden="1">
+    <row r="89" spans="1:16">
       <c r="A89" t="s">
         <v>259</v>
       </c>
@@ -20293,7 +20280,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1">
+    <row r="90" spans="1:16">
       <c r="A90" s="7" t="s">
         <v>263</v>
       </c>
@@ -20343,7 +20330,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1">
+    <row r="91" spans="1:16">
       <c r="A91" s="7" t="s">
         <v>267</v>
       </c>
@@ -20391,7 +20378,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1">
+    <row r="92" spans="1:16">
       <c r="A92" s="7" t="s">
         <v>269</v>
       </c>
@@ -20439,7 +20426,7 @@
         <v>848000</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1">
+    <row r="93" spans="1:16" ht="16">
       <c r="A93" s="45" t="s">
         <v>272</v>
       </c>
@@ -20490,7 +20477,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1">
+    <row r="94" spans="1:16">
       <c r="A94" s="7" t="s">
         <v>276</v>
       </c>
@@ -20541,7 +20528,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1">
+    <row r="95" spans="1:16" ht="16">
       <c r="A95" t="s">
         <v>279</v>
       </c>
@@ -20590,7 +20577,7 @@
       </c>
       <c r="P95" s="7"/>
     </row>
-    <row r="96" spans="1:16" hidden="1">
+    <row r="96" spans="1:16">
       <c r="A96" t="s">
         <v>282</v>
       </c>
@@ -20641,7 +20628,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1">
+    <row r="97" spans="1:16">
       <c r="A97" t="s">
         <v>285</v>
       </c>
@@ -20692,7 +20679,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1">
+    <row r="98" spans="1:16">
       <c r="A98" s="7" t="s">
         <v>288</v>
       </c>
@@ -20742,7 +20729,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1">
+    <row r="99" spans="1:16">
       <c r="A99" t="s">
         <v>291</v>
       </c>
@@ -20793,7 +20780,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1">
+    <row r="100" spans="1:16" ht="16">
       <c r="A100" t="s">
         <v>294</v>
       </c>
@@ -20844,7 +20831,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1">
+    <row r="101" spans="1:16">
       <c r="A101" s="7" t="s">
         <v>298</v>
       </c>
@@ -20895,7 +20882,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1">
+    <row r="102" spans="1:16">
       <c r="A102" s="44" t="s">
         <v>301</v>
       </c>
@@ -20940,7 +20927,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1">
+    <row r="103" spans="1:16">
       <c r="A103" s="44" t="s">
         <v>303</v>
       </c>
@@ -20985,7 +20972,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1">
+    <row r="104" spans="1:16">
       <c r="A104" t="s">
         <v>305</v>
       </c>
@@ -21030,7 +21017,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="105" spans="1:16" hidden="1">
+    <row r="105" spans="1:16">
       <c r="A105" t="s">
         <v>308</v>
       </c>
@@ -21081,7 +21068,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="106" spans="1:16" hidden="1">
+    <row r="106" spans="1:16">
       <c r="A106" s="7" t="s">
         <v>311</v>
       </c>
@@ -21132,7 +21119,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1">
+    <row r="107" spans="1:16" ht="16">
       <c r="A107" s="7" t="s">
         <v>316</v>
       </c>
@@ -21182,7 +21169,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="108" spans="1:16" hidden="1">
+    <row r="108" spans="1:16">
       <c r="A108" s="7" t="s">
         <v>319</v>
       </c>
@@ -21232,7 +21219,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="109" spans="1:16" hidden="1">
+    <row r="109" spans="1:16">
       <c r="A109" s="7" t="s">
         <v>322</v>
       </c>
@@ -21280,7 +21267,7 @@
         <v>999000</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1">
+    <row r="110" spans="1:16">
       <c r="A110" s="7" t="s">
         <v>323</v>
       </c>
@@ -21328,7 +21315,7 @@
         <v>49905</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1">
+    <row r="111" spans="1:16">
       <c r="A111" t="s">
         <v>326</v>
       </c>
@@ -21376,7 +21363,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1">
+    <row r="112" spans="1:16" ht="16">
       <c r="A112" s="7" t="s">
         <v>328</v>
       </c>
@@ -21426,7 +21413,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="113" spans="1:16" hidden="1">
+    <row r="113" spans="1:16">
       <c r="A113" s="7" t="s">
         <v>333</v>
       </c>
@@ -21476,7 +21463,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="114" spans="1:16" hidden="1">
+    <row r="114" spans="1:16">
       <c r="A114" s="7" t="s">
         <v>334</v>
       </c>
@@ -21524,7 +21511,7 @@
         <v>42480</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1">
+    <row r="115" spans="1:16">
       <c r="A115" s="7" t="s">
         <v>338</v>
       </c>
@@ -21572,7 +21559,7 @@
         <v>5099.8</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1">
+    <row r="116" spans="1:16">
       <c r="A116" s="7" t="s">
         <v>340</v>
       </c>
@@ -21623,7 +21610,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1">
+    <row r="117" spans="1:16">
       <c r="A117" s="7" t="s">
         <v>344</v>
       </c>
@@ -21674,7 +21661,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1">
+    <row r="118" spans="1:16">
       <c r="A118" t="s">
         <v>348</v>
       </c>
@@ -21722,7 +21709,7 @@
         <v>1355572</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1">
+    <row r="119" spans="1:16">
       <c r="A119" t="s">
         <v>352</v>
       </c>
@@ -21773,7 +21760,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="120" spans="1:16" hidden="1">
+    <row r="120" spans="1:16">
       <c r="A120" t="s">
         <v>355</v>
       </c>
@@ -21824,7 +21811,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1">
+    <row r="121" spans="1:16">
       <c r="A121" t="s">
         <v>358</v>
       </c>
@@ -21872,7 +21859,7 @@
         <v>16952</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1">
+    <row r="122" spans="1:16">
       <c r="A122" s="7" t="s">
         <v>360</v>
       </c>
@@ -21923,7 +21910,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1">
+    <row r="123" spans="1:16">
       <c r="A123" s="7" t="s">
         <v>364</v>
       </c>
@@ -21974,7 +21961,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1">
+    <row r="124" spans="1:16">
       <c r="A124" t="s">
         <v>365</v>
       </c>
@@ -22025,7 +22012,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1">
+    <row r="125" spans="1:16">
       <c r="A125" t="s">
         <v>370</v>
       </c>
@@ -22076,7 +22063,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1">
+    <row r="126" spans="1:16">
       <c r="A126" t="s">
         <v>373</v>
       </c>
@@ -22127,7 +22114,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1">
+    <row r="127" spans="1:16">
       <c r="A127" t="s">
         <v>374</v>
       </c>
@@ -22178,7 +22165,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1">
+    <row r="128" spans="1:16">
       <c r="A128" t="s">
         <v>377</v>
       </c>
@@ -22229,7 +22216,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="129" spans="1:16" hidden="1">
+    <row r="129" spans="1:16">
       <c r="A129" t="s">
         <v>378</v>
       </c>
@@ -22280,7 +22267,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="130" spans="1:16" hidden="1">
+    <row r="130" spans="1:16">
       <c r="A130" t="s">
         <v>379</v>
       </c>
@@ -22331,7 +22318,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1">
+    <row r="131" spans="1:16">
       <c r="A131" s="15" t="s">
         <v>382</v>
       </c>
@@ -22382,7 +22369,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="132" spans="1:16" hidden="1">
+    <row r="132" spans="1:16">
       <c r="A132" s="88" t="s">
         <v>383</v>
       </c>
@@ -22433,7 +22420,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1">
+    <row r="133" spans="1:16" ht="16">
       <c r="A133" s="88" t="s">
         <v>386</v>
       </c>
@@ -22476,7 +22463,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="134" spans="1:16" hidden="1">
+    <row r="134" spans="1:16" ht="16">
       <c r="A134" s="88" t="s">
         <v>386</v>
       </c>
@@ -22519,7 +22506,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1">
+    <row r="135" spans="1:16">
       <c r="A135" t="s">
         <v>389</v>
       </c>
@@ -22567,7 +22554,7 @@
         <v>258000</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1">
+    <row r="136" spans="1:16">
       <c r="A136" s="33" t="s">
         <v>390</v>
       </c>
@@ -22600,7 +22587,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="137" spans="1:16" hidden="1">
+    <row r="137" spans="1:16">
       <c r="A137" t="s">
         <v>391</v>
       </c>
@@ -22648,7 +22635,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="138" spans="1:16" hidden="1">
+    <row r="138" spans="1:16">
       <c r="A138" t="s">
         <v>393</v>
       </c>
@@ -22699,7 +22686,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="139" spans="1:16" hidden="1">
+    <row r="139" spans="1:16">
       <c r="A139" s="33" t="s">
         <v>397</v>
       </c>
@@ -22750,7 +22737,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1">
+    <row r="140" spans="1:16">
       <c r="A140" t="s">
         <v>399</v>
       </c>
@@ -22801,7 +22788,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="141" spans="1:16" hidden="1">
+    <row r="141" spans="1:16">
       <c r="A141" t="s">
         <v>401</v>
       </c>
@@ -22849,7 +22836,7 @@
         <v>12679.68</v>
       </c>
     </row>
-    <row r="142" spans="1:16" hidden="1">
+    <row r="142" spans="1:16">
       <c r="A142" t="s">
         <v>404</v>
       </c>
@@ -22897,7 +22884,7 @@
         <v>10821.12</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1">
+    <row r="143" spans="1:16">
       <c r="A143" t="s">
         <v>406</v>
       </c>
@@ -22945,7 +22932,7 @@
         <v>6959.36</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1">
+    <row r="144" spans="1:16">
       <c r="A144" t="s">
         <v>408</v>
       </c>
@@ -22993,7 +22980,7 @@
         <v>5410.56</v>
       </c>
     </row>
-    <row r="145" spans="1:16" hidden="1">
+    <row r="145" spans="1:16">
       <c r="A145" t="s">
         <v>410</v>
       </c>
@@ -23041,7 +23028,7 @@
         <v>4590.72</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1">
+    <row r="146" spans="1:16">
       <c r="A146" s="88" t="s">
         <v>412</v>
       </c>
@@ -23090,7 +23077,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="147" spans="1:16" hidden="1">
+    <row r="147" spans="1:16">
       <c r="A147" t="s">
         <v>415</v>
       </c>
@@ -23138,7 +23125,7 @@
         <v>2040.32</v>
       </c>
     </row>
-    <row r="148" spans="1:16" hidden="1">
+    <row r="148" spans="1:16">
       <c r="A148" t="s">
         <v>417</v>
       </c>
@@ -23186,7 +23173,7 @@
         <v>5720.32</v>
       </c>
     </row>
-    <row r="149" spans="1:16" hidden="1">
+    <row r="149" spans="1:16">
       <c r="A149" t="s">
         <v>419</v>
       </c>
@@ -23234,7 +23221,7 @@
         <v>8161</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1">
+    <row r="150" spans="1:16">
       <c r="A150" t="s">
         <v>421</v>
       </c>
@@ -23282,7 +23269,7 @@
         <v>5100.8</v>
       </c>
     </row>
-    <row r="151" spans="1:16" hidden="1">
+    <row r="151" spans="1:16">
       <c r="A151" t="s">
         <v>423</v>
       </c>
@@ -23330,7 +23317,7 @@
         <v>5100.8</v>
       </c>
     </row>
-    <row r="152" spans="1:16" hidden="1">
+    <row r="152" spans="1:16">
       <c r="A152" t="s">
         <v>425</v>
       </c>
@@ -23378,7 +23365,7 @@
         <v>10201.6</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1">
+    <row r="153" spans="1:16">
       <c r="A153" t="s">
         <v>427</v>
       </c>
@@ -23426,7 +23413,7 @@
         <v>5410.56</v>
       </c>
     </row>
-    <row r="154" spans="1:16" hidden="1">
+    <row r="154" spans="1:16">
       <c r="A154" s="88" t="s">
         <v>429</v>
       </c>
@@ -23475,7 +23462,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="155" spans="1:16" hidden="1">
+    <row r="155" spans="1:16">
       <c r="A155" t="s">
         <v>431</v>
       </c>
@@ -23523,7 +23510,7 @@
         <v>5410.56</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1">
+    <row r="156" spans="1:16">
       <c r="A156" t="s">
         <v>433</v>
       </c>
@@ -23571,7 +23558,7 @@
         <v>2860.16</v>
       </c>
     </row>
-    <row r="157" spans="1:16" hidden="1">
+    <row r="157" spans="1:16">
       <c r="A157" t="s">
         <v>435</v>
       </c>
@@ -23619,7 +23606,7 @@
         <v>2550.4</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1">
+    <row r="158" spans="1:16">
       <c r="A158" t="s">
         <v>437</v>
       </c>
@@ -23667,7 +23654,7 @@
         <v>2550.4</v>
       </c>
     </row>
-    <row r="159" spans="1:16" hidden="1">
+    <row r="159" spans="1:16">
       <c r="A159" t="s">
         <v>439</v>
       </c>
@@ -23715,7 +23702,7 @@
         <v>2860.16</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1">
+    <row r="160" spans="1:16">
       <c r="A160" t="s">
         <v>441</v>
       </c>
@@ -23763,7 +23750,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="161" spans="1:16" hidden="1">
+    <row r="161" spans="1:16">
       <c r="A161" t="s">
         <v>443</v>
       </c>
@@ -23814,7 +23801,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="162" spans="1:16" hidden="1">
+    <row r="162" spans="1:16">
       <c r="A162" t="s">
         <v>446</v>
       </c>
@@ -23865,7 +23852,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="163" spans="1:16" hidden="1">
+    <row r="163" spans="1:16">
       <c r="A163" t="s">
         <v>448</v>
       </c>
@@ -23913,7 +23900,7 @@
         <v>11900</v>
       </c>
     </row>
-    <row r="164" spans="1:16" hidden="1">
+    <row r="164" spans="1:16">
       <c r="A164" t="s">
         <v>450</v>
       </c>
@@ -23961,7 +23948,7 @@
         <v>93772</v>
       </c>
     </row>
-    <row r="165" spans="1:16" hidden="1">
+    <row r="165" spans="1:16">
       <c r="A165" t="s">
         <v>453</v>
       </c>
@@ -24012,7 +23999,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="166" spans="1:16" hidden="1">
+    <row r="166" spans="1:16">
       <c r="A166" t="s">
         <v>456</v>
       </c>
@@ -24063,7 +24050,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="167" spans="1:16" hidden="1">
+    <row r="167" spans="1:16">
       <c r="A167" t="s">
         <v>458</v>
       </c>
@@ -24146,7 +24133,7 @@
         <v>46174</v>
       </c>
       <c r="K168" s="42">
-        <v>46387</v>
+        <v>46752</v>
       </c>
       <c r="L168" s="35" t="s">
         <v>191</v>
@@ -24162,7 +24149,7 @@
         <v>42861.279999999999</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1">
+    <row r="169" spans="1:16">
       <c r="A169" t="s">
         <v>462</v>
       </c>
@@ -24213,7 +24200,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="170" spans="1:16" hidden="1">
+    <row r="170" spans="1:16">
       <c r="A170" t="s">
         <v>465</v>
       </c>
@@ -24261,7 +24248,7 @@
         <v>56108.800000000003</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1">
+    <row r="171" spans="1:16">
       <c r="A171" t="s">
         <v>467</v>
       </c>
@@ -24309,7 +24296,7 @@
         <v>4080.64</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1">
+    <row r="172" spans="1:16">
       <c r="A172" t="s">
         <v>469</v>
       </c>
@@ -24360,7 +24347,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1">
+    <row r="173" spans="1:16">
       <c r="A173" t="s">
         <v>472</v>
       </c>
@@ -24411,7 +24398,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="174" spans="1:16" hidden="1">
+    <row r="174" spans="1:16">
       <c r="A174" t="s">
         <v>474</v>
       </c>
@@ -24459,7 +24446,7 @@
         <v>14234</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1">
+    <row r="175" spans="1:16" ht="16">
       <c r="A175" t="s">
         <v>476</v>
       </c>
@@ -24504,7 +24491,7 @@
         <v>29148</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1">
+    <row r="176" spans="1:16">
       <c r="A176" t="s">
         <v>478</v>
       </c>
@@ -24552,7 +24539,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="177" spans="1:16" hidden="1">
+    <row r="177" spans="1:16">
       <c r="A177" t="s">
         <v>481</v>
       </c>
@@ -24600,7 +24587,7 @@
         <v>86549</v>
       </c>
     </row>
-    <row r="178" spans="1:16" hidden="1">
+    <row r="178" spans="1:16">
       <c r="A178" t="s">
         <v>483</v>
       </c>
@@ -24651,7 +24638,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="179" spans="1:16" hidden="1">
+    <row r="179" spans="1:16">
       <c r="A179" t="s">
         <v>484</v>
       </c>
@@ -24702,7 +24689,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="180" spans="1:16" hidden="1">
+    <row r="180" spans="1:16">
       <c r="A180" t="s">
         <v>487</v>
       </c>
@@ -24750,7 +24737,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="181" spans="1:16" hidden="1">
+    <row r="181" spans="1:16">
       <c r="A181" t="s">
         <v>489</v>
       </c>
@@ -24793,7 +24780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:16" hidden="1">
+    <row r="182" spans="1:16">
       <c r="A182" t="s">
         <v>490</v>
       </c>
@@ -24841,7 +24828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:16" hidden="1">
+    <row r="183" spans="1:16">
       <c r="A183" t="s">
         <v>492</v>
       </c>
@@ -24889,7 +24876,7 @@
         <v>3774</v>
       </c>
     </row>
-    <row r="184" spans="1:16" hidden="1">
+    <row r="184" spans="1:16">
       <c r="A184" t="s">
         <v>493</v>
       </c>
@@ -24936,7 +24923,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="185" spans="1:16" hidden="1">
+    <row r="185" spans="1:16">
       <c r="A185" t="s">
         <v>496</v>
       </c>
@@ -24981,7 +24968,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="186" spans="1:16" hidden="1">
+    <row r="186" spans="1:16">
       <c r="A186" t="s">
         <v>498</v>
       </c>
@@ -25023,7 +25010,7 @@
         <v>37500</v>
       </c>
     </row>
-    <row r="187" spans="1:16" hidden="1">
+    <row r="187" spans="1:16" ht="16">
       <c r="A187" s="88" t="s">
         <v>499</v>
       </c>
@@ -25064,7 +25051,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="188" spans="1:16" hidden="1">
+    <row r="188" spans="1:16">
       <c r="A188" t="s">
         <v>499</v>
       </c>
@@ -25112,7 +25099,7 @@
         <v>1275.2</v>
       </c>
     </row>
-    <row r="189" spans="1:16" hidden="1">
+    <row r="189" spans="1:16">
       <c r="A189" t="s">
         <v>499</v>
       </c>
@@ -25160,7 +25147,7 @@
         <v>1275.2</v>
       </c>
     </row>
-    <row r="190" spans="1:16" hidden="1">
+    <row r="190" spans="1:16" ht="16">
       <c r="A190" s="136" t="s">
         <v>506</v>
       </c>
@@ -25236,399 +25223,388 @@
       <c r="L205" s="35"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P190" xr:uid="{1C13DAFA-355F-44D5-B195-6558516D42F2}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Hosting"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Hana Sinska"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:P190" xr:uid="{1C13DAFA-355F-44D5-B195-6558516D42F2}"/>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="A43:B44">
-    <cfRule type="expression" dxfId="180" priority="116">
+    <cfRule type="expression" dxfId="170" priority="116">
       <formula>#REF!="check"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A61:B61">
-    <cfRule type="expression" dxfId="179" priority="101">
+    <cfRule type="expression" dxfId="169" priority="101">
       <formula>#REF!="check"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B62">
-    <cfRule type="expression" dxfId="178" priority="91">
+    <cfRule type="expression" dxfId="168" priority="91">
       <formula>#REF!="check"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1">
-    <cfRule type="duplicateValues" dxfId="177" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2">
-    <cfRule type="duplicateValues" dxfId="176" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="duplicateValues" dxfId="174" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="duplicateValues" dxfId="172" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="171" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="199"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="duplicateValues" dxfId="170" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6">
-    <cfRule type="duplicateValues" dxfId="168" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7">
-    <cfRule type="duplicateValues" dxfId="166" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8">
-    <cfRule type="duplicateValues" dxfId="164" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="187"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9">
-    <cfRule type="duplicateValues" dxfId="162" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10">
-    <cfRule type="duplicateValues" dxfId="160" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11">
-    <cfRule type="duplicateValues" dxfId="158" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G12">
-    <cfRule type="duplicateValues" dxfId="156" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="175"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G13">
-    <cfRule type="duplicateValues" dxfId="154" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G14">
-    <cfRule type="duplicateValues" dxfId="152" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G15">
-    <cfRule type="duplicateValues" dxfId="150" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G16">
-    <cfRule type="duplicateValues" dxfId="148" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="163"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G17">
-    <cfRule type="duplicateValues" dxfId="146" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G18:G19">
-    <cfRule type="duplicateValues" dxfId="144" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25">
-    <cfRule type="duplicateValues" dxfId="142" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26:G27">
-    <cfRule type="duplicateValues" dxfId="140" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="duplicateValues" dxfId="138" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="145"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G29:G30">
-    <cfRule type="duplicateValues" dxfId="136" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="141"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G31">
-    <cfRule type="duplicateValues" dxfId="134" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="139"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G32">
-    <cfRule type="duplicateValues" dxfId="132" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="136"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="duplicateValues" dxfId="130" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G35">
-    <cfRule type="duplicateValues" dxfId="128" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G36">
-    <cfRule type="duplicateValues" dxfId="126" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="82"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G37">
-    <cfRule type="duplicateValues" dxfId="124" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G38">
-    <cfRule type="duplicateValues" dxfId="122" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G39">
-    <cfRule type="duplicateValues" dxfId="120" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40">
-    <cfRule type="duplicateValues" dxfId="118" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="126"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41">
-    <cfRule type="duplicateValues" dxfId="116" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G42">
-    <cfRule type="duplicateValues" dxfId="114" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G43:G44">
-    <cfRule type="duplicateValues" dxfId="112" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G46">
-    <cfRule type="duplicateValues" dxfId="110" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G47">
-    <cfRule type="duplicateValues" dxfId="108" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G48">
-    <cfRule type="duplicateValues" dxfId="106" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G49">
-    <cfRule type="duplicateValues" dxfId="104" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G50">
-    <cfRule type="duplicateValues" dxfId="102" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51">
-    <cfRule type="duplicateValues" dxfId="100" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G52">
-    <cfRule type="duplicateValues" dxfId="98" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G54">
-    <cfRule type="duplicateValues" dxfId="96" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G57">
-    <cfRule type="duplicateValues" dxfId="94" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G61">
-    <cfRule type="duplicateValues" dxfId="92" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="207"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G62">
-    <cfRule type="duplicateValues" dxfId="90" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G63">
-    <cfRule type="duplicateValues" dxfId="88" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G65">
-    <cfRule type="duplicateValues" dxfId="86" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G66">
-    <cfRule type="duplicateValues" dxfId="84" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G68">
-    <cfRule type="duplicateValues" dxfId="82" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G69:G70 G64 G76">
-    <cfRule type="duplicateValues" dxfId="80" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="209"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G71">
-    <cfRule type="duplicateValues" dxfId="79" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G72">
-    <cfRule type="duplicateValues" dxfId="77" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G73">
-    <cfRule type="duplicateValues" dxfId="75" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G75">
-    <cfRule type="duplicateValues" dxfId="73" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G82">
-    <cfRule type="duplicateValues" dxfId="71" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G84">
-    <cfRule type="duplicateValues" dxfId="69" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G86">
-    <cfRule type="duplicateValues" dxfId="67" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G89:G90 G83 G85 G77:G81">
-    <cfRule type="duplicateValues" dxfId="65" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="212"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G92">
-    <cfRule type="duplicateValues" dxfId="63" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G94">
-    <cfRule type="duplicateValues" dxfId="61" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G100">
-    <cfRule type="duplicateValues" dxfId="59" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G103">
-    <cfRule type="duplicateValues" dxfId="57" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G106">
-    <cfRule type="duplicateValues" dxfId="55" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G107">
-    <cfRule type="duplicateValues" dxfId="53" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G114">
-    <cfRule type="duplicateValues" dxfId="51" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G118">
-    <cfRule type="duplicateValues" dxfId="49" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G120">
-    <cfRule type="duplicateValues" dxfId="47" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G121">
-    <cfRule type="duplicateValues" dxfId="45" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G124">
-    <cfRule type="duplicateValues" dxfId="43" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G130">
-    <cfRule type="duplicateValues" dxfId="41" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G132">
-    <cfRule type="duplicateValues" dxfId="39" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="duplicateValues" dxfId="37" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="205"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="duplicateValues" dxfId="36" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="204"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="35" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="duplicateValues" dxfId="34" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="duplicateValues" dxfId="33" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7">
-    <cfRule type="duplicateValues" dxfId="32" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H8">
-    <cfRule type="duplicateValues" dxfId="31" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9">
-    <cfRule type="duplicateValues" dxfId="30" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10">
-    <cfRule type="duplicateValues" dxfId="29" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="28" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="27" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="26" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="171"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14">
-    <cfRule type="duplicateValues" dxfId="25" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15">
-    <cfRule type="duplicateValues" dxfId="24" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="23" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="162"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H18">
-    <cfRule type="duplicateValues" dxfId="21" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H19">
-    <cfRule type="duplicateValues" dxfId="20" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23:H24 H20:H21">
-    <cfRule type="duplicateValues" dxfId="19" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="18" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="149"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="17" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="146"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H28">
-    <cfRule type="duplicateValues" dxfId="16" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29">
-    <cfRule type="duplicateValues" dxfId="15" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30">
-    <cfRule type="duplicateValues" dxfId="14" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33">
-    <cfRule type="duplicateValues" dxfId="13" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H50">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H104:H112 H56 H48:H49 H32 H59:H64 H34:H46 H66:H69 H86 H88:H101 H51:H54 H71 H73:H83">
-    <cfRule type="duplicateValues" dxfId="11" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H172:H173">
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -25682,35 +25658,35 @@
     <tabColor rgb="FFFCDE92"/>
   </sheetPr>
   <dimension ref="A1:AA128"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" outlineLevelCol="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="59.453125" customWidth="1"/>
+    <col min="1" max="1" width="59.5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="4" width="17.54296875" customWidth="1"/>
-    <col min="5" max="5" width="7.54296875" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" customWidth="1"/>
-    <col min="7" max="7" width="15.81640625" style="40" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="16.26953125" style="40" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="12.90625" style="40" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="15.54296875" style="40" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="13.7265625" style="40" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="11.453125" style="40" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="12.54296875" style="40" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="20.54296875" style="40" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="12.54296875" style="40" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="20.54296875" style="40" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="7.5" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" style="40" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="16.33203125" style="40" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="12.83203125" style="40" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="15.5" style="40" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="13.6640625" style="40" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="11.5" style="40" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="12.5" style="40" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="20.5" style="40" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="12.5" style="40" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="20.5" style="40" customWidth="1" outlineLevel="1"/>
     <col min="17" max="17" width="15" style="40" customWidth="1"/>
-    <col min="18" max="18" width="18.54296875" style="40" customWidth="1"/>
-    <col min="19" max="20" width="10.1796875" style="40" customWidth="1"/>
-    <col min="21" max="21" width="10.1796875" customWidth="1"/>
+    <col min="18" max="18" width="18.5" style="40" customWidth="1"/>
+    <col min="19" max="20" width="10.1640625" style="40" customWidth="1"/>
+    <col min="21" max="21" width="10.1640625" customWidth="1"/>
     <col min="22" max="22" width="10" style="40" customWidth="1"/>
-    <col min="23" max="23" width="9.1796875" customWidth="1"/>
-    <col min="24" max="24" width="9.1796875" style="43" customWidth="1"/>
-    <col min="25" max="26" width="9.1796875" customWidth="1"/>
-    <col min="27" max="27" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.1640625" customWidth="1"/>
+    <col min="24" max="24" width="9.1640625" style="43" customWidth="1"/>
+    <col min="25" max="26" width="9.1640625" customWidth="1"/>
+    <col min="27" max="27" width="37.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="38.15" customHeight="1">
+    <row r="1" spans="1:27" ht="38.25" customHeight="1">
       <c r="A1" s="102" t="s">
         <v>1</v>
       </c>
@@ -25793,7 +25769,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="14.5" hidden="1">
+    <row r="2" spans="1:27" hidden="1">
       <c r="A2" s="41" t="s">
         <v>62</v>
       </c>
@@ -25841,7 +25817,7 @@
       <c r="V2"/>
       <c r="X2"/>
     </row>
-    <row r="3" spans="1:27" ht="14.5" hidden="1">
+    <row r="3" spans="1:27" hidden="1">
       <c r="A3" s="41" t="s">
         <v>65</v>
       </c>
@@ -25889,7 +25865,7 @@
       <c r="V3"/>
       <c r="X3"/>
     </row>
-    <row r="4" spans="1:27" ht="14.5" hidden="1">
+    <row r="4" spans="1:27" hidden="1">
       <c r="A4" s="41" t="s">
         <v>68</v>
       </c>
@@ -25937,7 +25913,7 @@
       <c r="V4"/>
       <c r="X4"/>
     </row>
-    <row r="5" spans="1:27" ht="14.5" hidden="1">
+    <row r="5" spans="1:27" hidden="1">
       <c r="A5" s="33" t="s">
         <v>51</v>
       </c>
@@ -25994,7 +25970,7 @@
       </c>
       <c r="Y5" s="40"/>
     </row>
-    <row r="6" spans="1:27" ht="14.5" hidden="1">
+    <row r="6" spans="1:27" hidden="1">
       <c r="A6" s="33" t="s">
         <v>57</v>
       </c>
@@ -26041,7 +26017,7 @@
       <c r="V6"/>
       <c r="X6"/>
     </row>
-    <row r="7" spans="1:27" ht="14.5" hidden="1">
+    <row r="7" spans="1:27" hidden="1">
       <c r="A7" s="33" t="s">
         <v>115</v>
       </c>
@@ -26089,7 +26065,7 @@
       <c r="V7"/>
       <c r="X7"/>
     </row>
-    <row r="8" spans="1:27" ht="14.5" hidden="1">
+    <row r="8" spans="1:27" hidden="1">
       <c r="A8" s="41" t="s">
         <v>125</v>
       </c>
@@ -26139,7 +26115,7 @@
       <c r="V8"/>
       <c r="X8"/>
     </row>
-    <row r="9" spans="1:27" ht="14.5" hidden="1">
+    <row r="9" spans="1:27" hidden="1">
       <c r="A9" s="41" t="s">
         <v>128</v>
       </c>
@@ -26189,7 +26165,7 @@
       <c r="V9"/>
       <c r="X9"/>
     </row>
-    <row r="10" spans="1:27" ht="14.5" hidden="1">
+    <row r="10" spans="1:27" hidden="1">
       <c r="A10" s="41" t="s">
         <v>132</v>
       </c>
@@ -26239,7 +26215,7 @@
       <c r="V10"/>
       <c r="X10"/>
     </row>
-    <row r="11" spans="1:27" ht="14.5" hidden="1">
+    <row r="11" spans="1:27" hidden="1">
       <c r="A11" s="33" t="s">
         <v>148</v>
       </c>
@@ -26292,7 +26268,7 @@
       <c r="V11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:27" ht="14.5" hidden="1">
+    <row r="12" spans="1:27" hidden="1">
       <c r="A12" s="33" t="s">
         <v>361</v>
       </c>
@@ -26354,7 +26330,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="14.5" hidden="1">
+    <row r="13" spans="1:27" hidden="1">
       <c r="A13" s="41" t="s">
         <v>76</v>
       </c>
@@ -26414,7 +26390,7 @@
       <c r="W13" s="40"/>
       <c r="X13"/>
     </row>
-    <row r="14" spans="1:27" ht="14.5" hidden="1">
+    <row r="14" spans="1:27" hidden="1">
       <c r="A14" s="41" t="s">
         <v>80</v>
       </c>
@@ -26476,7 +26452,7 @@
       </c>
       <c r="Y14" s="40"/>
     </row>
-    <row r="15" spans="1:27" ht="14.5" hidden="1">
+    <row r="15" spans="1:27" hidden="1">
       <c r="A15" s="41" t="s">
         <v>263</v>
       </c>
@@ -26534,7 +26510,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="14.5" hidden="1">
+    <row r="16" spans="1:27" hidden="1">
       <c r="A16" s="41" t="s">
         <v>267</v>
       </c>
@@ -26591,7 +26567,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="14.5" hidden="1">
+    <row r="17" spans="1:27" hidden="1">
       <c r="A17" s="41" t="s">
         <v>276</v>
       </c>
@@ -26645,7 +26621,7 @@
       <c r="V17"/>
       <c r="X17"/>
     </row>
-    <row r="18" spans="1:27" ht="14.5" hidden="1">
+    <row r="18" spans="1:27" hidden="1">
       <c r="A18" s="33" t="s">
         <v>279</v>
       </c>
@@ -26699,7 +26675,7 @@
       <c r="W18" s="40"/>
       <c r="X18"/>
     </row>
-    <row r="19" spans="1:27" ht="14.5" hidden="1">
+    <row r="19" spans="1:27" hidden="1">
       <c r="A19" t="s">
         <v>286</v>
       </c>
@@ -26753,7 +26729,7 @@
       <c r="W19" s="40"/>
       <c r="X19"/>
     </row>
-    <row r="20" spans="1:27" ht="14.5" hidden="1">
+    <row r="20" spans="1:27" hidden="1">
       <c r="A20" t="s">
         <v>283</v>
       </c>
@@ -26807,7 +26783,7 @@
       <c r="V20"/>
       <c r="X20"/>
     </row>
-    <row r="21" spans="1:27" ht="14.5" hidden="1">
+    <row r="21" spans="1:27" hidden="1">
       <c r="A21" s="41" t="s">
         <v>288</v>
       </c>
@@ -26864,7 +26840,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="14.5" hidden="1">
+    <row r="22" spans="1:27" hidden="1">
       <c r="A22" s="33" t="s">
         <v>291</v>
       </c>
@@ -26918,7 +26894,7 @@
       <c r="V22"/>
       <c r="X22"/>
     </row>
-    <row r="23" spans="1:27" ht="14.5" hidden="1">
+    <row r="23" spans="1:27" hidden="1">
       <c r="A23" s="33" t="s">
         <v>294</v>
       </c>
@@ -26972,7 +26948,7 @@
       <c r="V23"/>
       <c r="X23"/>
     </row>
-    <row r="24" spans="1:27" ht="14.5" hidden="1">
+    <row r="24" spans="1:27" hidden="1">
       <c r="A24" s="41" t="s">
         <v>312</v>
       </c>
@@ -27036,7 +27012,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="14.5" hidden="1">
+    <row r="25" spans="1:27" hidden="1">
       <c r="A25" s="41" t="s">
         <v>316</v>
       </c>
@@ -27090,7 +27066,7 @@
       <c r="V25"/>
       <c r="X25"/>
     </row>
-    <row r="26" spans="1:27" ht="14.5" hidden="1">
+    <row r="26" spans="1:27" hidden="1">
       <c r="A26" s="41" t="s">
         <v>561</v>
       </c>
@@ -27148,7 +27124,7 @@
       </c>
       <c r="Y26" s="40"/>
     </row>
-    <row r="27" spans="1:27" ht="14.5" hidden="1">
+    <row r="27" spans="1:27" hidden="1">
       <c r="A27" s="41" t="s">
         <v>328</v>
       </c>
@@ -27203,7 +27179,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="14.5" hidden="1">
+    <row r="28" spans="1:27" hidden="1">
       <c r="A28" s="41" t="s">
         <v>333</v>
       </c>
@@ -27258,7 +27234,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="14.5" hidden="1">
+    <row r="29" spans="1:27" hidden="1">
       <c r="A29" s="41" t="s">
         <v>335</v>
       </c>
@@ -27316,7 +27292,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="14.5" hidden="1">
+    <row r="30" spans="1:27" hidden="1">
       <c r="A30" s="41" t="s">
         <v>338</v>
       </c>
@@ -27366,7 +27342,7 @@
       <c r="V30"/>
       <c r="X30"/>
     </row>
-    <row r="31" spans="1:27" ht="14.5" hidden="1">
+    <row r="31" spans="1:27" hidden="1">
       <c r="A31" s="95" t="s">
         <v>341</v>
       </c>
@@ -27408,7 +27384,7 @@
       <c r="V31"/>
       <c r="X31"/>
     </row>
-    <row r="32" spans="1:27" ht="14.5" hidden="1">
+    <row r="32" spans="1:27" hidden="1">
       <c r="A32" t="s">
         <v>441</v>
       </c>
@@ -27455,7 +27431,7 @@
       <c r="U32" s="49"/>
       <c r="Y32" s="40"/>
     </row>
-    <row r="33" spans="1:26" ht="14.5">
+    <row r="33" spans="1:26">
       <c r="A33" s="33" t="s">
         <v>166</v>
       </c>
@@ -27520,7 +27496,7 @@
       <c r="W33" s="40"/>
       <c r="X33"/>
     </row>
-    <row r="34" spans="1:26" ht="14.5" hidden="1">
+    <row r="34" spans="1:26" hidden="1">
       <c r="A34" t="s">
         <v>402</v>
       </c>
@@ -27560,7 +27536,7 @@
       <c r="W34" s="40"/>
       <c r="X34"/>
     </row>
-    <row r="35" spans="1:26" ht="14.5">
+    <row r="35" spans="1:26">
       <c r="A35" s="33" t="s">
         <v>171</v>
       </c>
@@ -27616,7 +27592,7 @@
       <c r="V35"/>
       <c r="X35"/>
     </row>
-    <row r="36" spans="1:26" ht="14.5">
+    <row r="36" spans="1:26">
       <c r="A36" s="33" t="s">
         <v>799</v>
       </c>
@@ -27649,7 +27625,7 @@
       <c r="K36" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="L36" s="150" t="s">
+      <c r="L36" s="11" t="s">
         <v>570</v>
       </c>
       <c r="M36" s="11"/>
@@ -27664,7 +27640,7 @@
       <c r="V36"/>
       <c r="X36"/>
     </row>
-    <row r="37" spans="1:26" ht="14.5">
+    <row r="37" spans="1:26">
       <c r="A37" s="33" t="s">
         <v>162</v>
       </c>
@@ -27724,7 +27700,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="14.5">
+    <row r="38" spans="1:26">
       <c r="A38" t="s">
         <v>168</v>
       </c>
@@ -27773,7 +27749,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="14.5">
+    <row r="39" spans="1:26">
       <c r="A39" s="87" t="s">
         <v>175</v>
       </c>
@@ -27824,7 +27800,7 @@
       </c>
       <c r="Y39" s="40"/>
     </row>
-    <row r="40" spans="1:26" ht="14.5">
+    <row r="40" spans="1:26">
       <c r="A40" s="33" t="s">
         <v>195</v>
       </c>
@@ -27876,7 +27852,7 @@
       <c r="V40"/>
       <c r="X40"/>
     </row>
-    <row r="41" spans="1:26" ht="14.5">
+    <row r="41" spans="1:26">
       <c r="A41" s="87" t="s">
         <v>198</v>
       </c>
@@ -27920,7 +27896,7 @@
       <c r="V41"/>
       <c r="X41"/>
     </row>
-    <row r="42" spans="1:26" ht="14.5">
+    <row r="42" spans="1:26">
       <c r="A42" s="87" t="s">
         <v>177</v>
       </c>
@@ -27973,7 +27949,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="43" spans="1:26" ht="14.5">
+    <row r="43" spans="1:26">
       <c r="A43" s="33" t="s">
         <v>181</v>
       </c>
@@ -28025,7 +28001,7 @@
       <c r="W43" s="40"/>
       <c r="Y43" s="40"/>
     </row>
-    <row r="44" spans="1:26" ht="14.5">
+    <row r="44" spans="1:26">
       <c r="A44" s="33" t="s">
         <v>219</v>
       </c>
@@ -28067,8 +28043,8 @@
       <c r="V44"/>
       <c r="X44"/>
     </row>
-    <row r="45" spans="1:26" ht="14.5">
-      <c r="A45" s="147" t="s">
+    <row r="45" spans="1:26">
+      <c r="A45" t="s">
         <v>795</v>
       </c>
       <c r="B45" s="53" t="str">
@@ -28126,7 +28102,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="14.5">
+    <row r="46" spans="1:26">
       <c r="A46" s="33" t="s">
         <v>216</v>
       </c>
@@ -28187,7 +28163,7 @@
       <c r="W46" s="40"/>
       <c r="Y46" s="40"/>
     </row>
-    <row r="47" spans="1:26" ht="14.5">
+    <row r="47" spans="1:26">
       <c r="A47" t="s">
         <v>389</v>
       </c>
@@ -28251,7 +28227,7 @@
       </c>
       <c r="Y47" s="40"/>
     </row>
-    <row r="48" spans="1:26" ht="14.5">
+    <row r="48" spans="1:26">
       <c r="A48" s="41" t="s">
         <v>245</v>
       </c>
@@ -28275,7 +28251,7 @@
         <f>VLOOKUP(A48,'Project List 2026'!B:I,8,0)</f>
         <v>Ongoing</v>
       </c>
-      <c r="G48" s="152" t="s">
+      <c r="G48" s="145" t="s">
         <v>584</v>
       </c>
       <c r="H48" s="110">
@@ -28305,7 +28281,7 @@
       <c r="V48"/>
       <c r="X48"/>
     </row>
-    <row r="49" spans="1:27" ht="14.5">
+    <row r="49" spans="1:27">
       <c r="A49" s="33" t="s">
         <v>225</v>
       </c>
@@ -28369,7 +28345,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="14.5">
+    <row r="50" spans="1:27">
       <c r="A50" s="33" t="s">
         <v>239</v>
       </c>
@@ -28425,8 +28401,8 @@
       <c r="W50" s="40"/>
       <c r="Y50" s="40"/>
     </row>
-    <row r="51" spans="1:27" ht="14.5">
-      <c r="A51" s="148" t="s">
+    <row r="51" spans="1:27">
+      <c r="A51" s="41" t="s">
         <v>796</v>
       </c>
       <c r="B51" s="53" t="str">
@@ -28486,8 +28462,8 @@
         <v>538</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="14.5">
-      <c r="A52" s="151" t="s">
+    <row r="52" spans="1:27">
+      <c r="A52" s="87" t="s">
         <v>259</v>
       </c>
       <c r="B52" s="53" t="str">
@@ -28537,8 +28513,8 @@
       <c r="W52" s="40"/>
       <c r="Y52" s="40"/>
     </row>
-    <row r="53" spans="1:27" ht="14.5">
-      <c r="A53" s="151" t="s">
+    <row r="53" spans="1:27">
+      <c r="A53" s="87" t="s">
         <v>229</v>
       </c>
       <c r="B53" s="53" t="str">
@@ -28580,7 +28556,7 @@
       <c r="W53" s="105"/>
       <c r="Y53" s="40"/>
     </row>
-    <row r="54" spans="1:27" ht="14.5">
+    <row r="54" spans="1:27">
       <c r="A54" s="87" t="s">
         <v>309</v>
       </c>
@@ -28631,7 +28607,7 @@
       <c r="V54"/>
       <c r="X54"/>
     </row>
-    <row r="55" spans="1:27" ht="14.5">
+    <row r="55" spans="1:27">
       <c r="A55" s="41" t="s">
         <v>344</v>
       </c>
@@ -28685,8 +28661,8 @@
       <c r="V55"/>
       <c r="X55"/>
     </row>
-    <row r="56" spans="1:27" ht="14.5">
-      <c r="A56" s="148" t="s">
+    <row r="56" spans="1:27">
+      <c r="A56" s="41" t="s">
         <v>797</v>
       </c>
       <c r="B56" s="53" t="str">
@@ -28746,7 +28722,7 @@
       <c r="W56" s="40"/>
       <c r="Y56" s="40"/>
     </row>
-    <row r="57" spans="1:27" ht="14.5">
+    <row r="57" spans="1:27">
       <c r="A57" t="s">
         <v>358</v>
       </c>
@@ -28796,7 +28772,7 @@
       <c r="V57"/>
       <c r="X57"/>
     </row>
-    <row r="58" spans="1:27" ht="14.5">
+    <row r="58" spans="1:27">
       <c r="A58" t="s">
         <v>355</v>
       </c>
@@ -28846,7 +28822,7 @@
       <c r="V58"/>
       <c r="X58"/>
     </row>
-    <row r="59" spans="1:27" ht="14.5">
+    <row r="59" spans="1:27">
       <c r="A59" s="33" t="s">
         <v>305</v>
       </c>
@@ -28892,7 +28868,7 @@
       <c r="W59" s="40"/>
       <c r="Y59" s="40"/>
     </row>
-    <row r="60" spans="1:27" ht="14.5">
+    <row r="60" spans="1:27">
       <c r="A60" s="33" t="s">
         <v>383</v>
       </c>
@@ -28946,7 +28922,7 @@
       <c r="V60"/>
       <c r="X60"/>
     </row>
-    <row r="61" spans="1:27" ht="14.5" hidden="1">
+    <row r="61" spans="1:27" hidden="1">
       <c r="A61" s="87" t="s">
         <v>17</v>
       </c>
@@ -29003,7 +28979,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="14.5" hidden="1">
+    <row r="62" spans="1:27" hidden="1">
       <c r="A62" s="41" t="s">
         <v>27</v>
       </c>
@@ -29063,7 +29039,7 @@
       <c r="V62"/>
       <c r="X62"/>
     </row>
-    <row r="63" spans="1:27" ht="14.5" hidden="1">
+    <row r="63" spans="1:27" hidden="1">
       <c r="A63" s="41" t="s">
         <v>34</v>
       </c>
@@ -29123,7 +29099,7 @@
       <c r="V63"/>
       <c r="X63"/>
     </row>
-    <row r="64" spans="1:27" ht="14.5" hidden="1">
+    <row r="64" spans="1:27" hidden="1">
       <c r="A64" s="87" t="s">
         <v>38</v>
       </c>
@@ -29176,7 +29152,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="14.5" hidden="1">
+    <row r="65" spans="1:27" hidden="1">
       <c r="A65" s="87" t="s">
         <v>42</v>
       </c>
@@ -29234,7 +29210,7 @@
       <c r="V65"/>
       <c r="X65"/>
     </row>
-    <row r="66" spans="1:27" ht="14.5" hidden="1">
+    <row r="66" spans="1:27" hidden="1">
       <c r="A66" s="33" t="s">
         <v>44</v>
       </c>
@@ -29291,7 +29267,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="14.5" hidden="1">
+    <row r="67" spans="1:27" hidden="1">
       <c r="A67" s="87" t="s">
         <v>47</v>
       </c>
@@ -29344,7 +29320,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="14.5" hidden="1">
+    <row r="68" spans="1:27" hidden="1">
       <c r="A68" s="41" t="s">
         <v>154</v>
       </c>
@@ -29408,7 +29384,7 @@
       <c r="V68"/>
       <c r="X68"/>
     </row>
-    <row r="69" spans="1:27" ht="14.5" hidden="1">
+    <row r="69" spans="1:27" hidden="1">
       <c r="A69" s="41" t="s">
         <v>156</v>
       </c>
@@ -29454,7 +29430,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="14.5" hidden="1">
+    <row r="70" spans="1:27" hidden="1">
       <c r="A70" s="41" t="s">
         <v>160</v>
       </c>
@@ -29511,7 +29487,7 @@
       <c r="V70"/>
       <c r="X70"/>
     </row>
-    <row r="71" spans="1:27" ht="14.5" hidden="1">
+    <row r="71" spans="1:27" hidden="1">
       <c r="A71" s="33" t="s">
         <v>200</v>
       </c>
@@ -29555,7 +29531,7 @@
       <c r="V71"/>
       <c r="X71"/>
     </row>
-    <row r="72" spans="1:27" ht="14.5" hidden="1">
+    <row r="72" spans="1:27" hidden="1">
       <c r="A72" s="33" t="s">
         <v>203</v>
       </c>
@@ -29614,7 +29590,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="14.5" hidden="1">
+    <row r="73" spans="1:27" hidden="1">
       <c r="A73" s="87" t="s">
         <v>204</v>
       </c>
@@ -29667,7 +29643,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="14.5" hidden="1">
+    <row r="74" spans="1:27" hidden="1">
       <c r="A74" s="41" t="s">
         <v>207</v>
       </c>
@@ -29725,7 +29701,7 @@
       <c r="V74"/>
       <c r="X74"/>
     </row>
-    <row r="75" spans="1:27" ht="14.5" hidden="1">
+    <row r="75" spans="1:27" hidden="1">
       <c r="A75" s="87" t="s">
         <v>210</v>
       </c>
@@ -29781,7 +29757,7 @@
       <c r="V75"/>
       <c r="X75"/>
     </row>
-    <row r="76" spans="1:27" ht="14.5" hidden="1">
+    <row r="76" spans="1:27" hidden="1">
       <c r="A76" s="33" t="s">
         <v>212</v>
       </c>
@@ -29841,7 +29817,7 @@
       <c r="V76"/>
       <c r="X76"/>
     </row>
-    <row r="77" spans="1:27" ht="14.5" hidden="1">
+    <row r="77" spans="1:27" hidden="1">
       <c r="A77" s="33" t="s">
         <v>214</v>
       </c>
@@ -29901,7 +29877,7 @@
       <c r="V77"/>
       <c r="X77"/>
     </row>
-    <row r="78" spans="1:27" ht="14.5" hidden="1">
+    <row r="78" spans="1:27" hidden="1">
       <c r="A78" s="41" t="s">
         <v>241</v>
       </c>
@@ -29962,7 +29938,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="14.5" hidden="1">
+    <row r="79" spans="1:27" hidden="1">
       <c r="A79" s="41" t="s">
         <v>249</v>
       </c>
@@ -30010,7 +29986,7 @@
       <c r="V79"/>
       <c r="X79"/>
     </row>
-    <row r="80" spans="1:27" ht="14.5" hidden="1">
+    <row r="80" spans="1:27" hidden="1">
       <c r="A80" s="41" t="s">
         <v>252</v>
       </c>
@@ -30067,7 +30043,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="14.5" hidden="1">
+    <row r="81" spans="1:27" hidden="1">
       <c r="A81" s="41" t="s">
         <v>253</v>
       </c>
@@ -30124,7 +30100,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="14.5" hidden="1">
+    <row r="82" spans="1:27" hidden="1">
       <c r="A82" s="41" t="s">
         <v>255</v>
       </c>
@@ -30182,7 +30158,7 @@
       <c r="V82"/>
       <c r="X82"/>
     </row>
-    <row r="83" spans="1:27" ht="14.5" hidden="1">
+    <row r="83" spans="1:27" hidden="1">
       <c r="A83" s="41" t="s">
         <v>270</v>
       </c>
@@ -30240,7 +30216,7 @@
       <c r="V83"/>
       <c r="X83"/>
     </row>
-    <row r="84" spans="1:27" ht="14.5" hidden="1">
+    <row r="84" spans="1:27" hidden="1">
       <c r="A84" s="33" t="s">
         <v>272</v>
       </c>
@@ -30282,7 +30258,7 @@
       <c r="V84"/>
       <c r="X84"/>
     </row>
-    <row r="85" spans="1:27" ht="14.5" hidden="1">
+    <row r="85" spans="1:27" hidden="1">
       <c r="A85" s="41" t="s">
         <v>322</v>
       </c>
@@ -30340,7 +30316,7 @@
       <c r="V85"/>
       <c r="X85"/>
     </row>
-    <row r="86" spans="1:27" ht="14.5" hidden="1">
+    <row r="86" spans="1:27" hidden="1">
       <c r="A86" s="41" t="s">
         <v>324</v>
       </c>
@@ -30398,7 +30374,7 @@
       <c r="V86"/>
       <c r="X86"/>
     </row>
-    <row r="87" spans="1:27" ht="14.5" hidden="1">
+    <row r="87" spans="1:27" hidden="1">
       <c r="A87" s="33" t="s">
         <v>370</v>
       </c>
@@ -30452,7 +30428,7 @@
       <c r="V87"/>
       <c r="X87"/>
     </row>
-    <row r="88" spans="1:27" ht="14.5" hidden="1">
+    <row r="88" spans="1:27" hidden="1">
       <c r="A88" s="33" t="s">
         <v>373</v>
       </c>
@@ -30506,7 +30482,7 @@
       <c r="V88"/>
       <c r="X88"/>
     </row>
-    <row r="89" spans="1:27" ht="14.5" hidden="1">
+    <row r="89" spans="1:27" hidden="1">
       <c r="A89" s="87" t="s">
         <v>375</v>
       </c>
@@ -30564,7 +30540,7 @@
       <c r="V89"/>
       <c r="X89"/>
     </row>
-    <row r="90" spans="1:27" ht="14.5" hidden="1">
+    <row r="90" spans="1:27" hidden="1">
       <c r="A90" s="33" t="s">
         <v>377</v>
       </c>
@@ -30621,7 +30597,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="14.5" hidden="1">
+    <row r="91" spans="1:27" hidden="1">
       <c r="A91" s="33" t="s">
         <v>378</v>
       </c>
@@ -30678,7 +30654,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="14.5" hidden="1">
+    <row r="92" spans="1:27" hidden="1">
       <c r="A92" s="87" t="s">
         <v>380</v>
       </c>
@@ -30734,7 +30710,7 @@
       <c r="V92"/>
       <c r="X92"/>
     </row>
-    <row r="93" spans="1:27" ht="14.5" hidden="1">
+    <row r="93" spans="1:27" hidden="1">
       <c r="A93" s="33" t="s">
         <v>382</v>
       </c>
@@ -30791,8 +30767,8 @@
         <v>623</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="14.5">
-      <c r="A94" s="149" t="s">
+    <row r="94" spans="1:27">
+      <c r="A94" s="33" t="s">
         <v>798</v>
       </c>
       <c r="B94" s="53" t="str">
@@ -30815,7 +30791,7 @@
         <f>VLOOKUP(A94,'Project List 2026'!B:I,8,0)</f>
         <v>Ongoing</v>
       </c>
-      <c r="G94" s="150" t="s">
+      <c r="G94" s="11" t="s">
         <v>533</v>
       </c>
       <c r="H94" s="110">
@@ -30857,7 +30833,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="14.5">
+    <row r="95" spans="1:27">
       <c r="A95" s="87" t="s">
         <v>366</v>
       </c>
@@ -30901,7 +30877,7 @@
       <c r="W95" s="40"/>
       <c r="Y95" s="40"/>
     </row>
-    <row r="96" spans="1:27" ht="14.5" hidden="1">
+    <row r="96" spans="1:27" hidden="1">
       <c r="A96" s="107" t="s">
         <v>448</v>
       </c>
@@ -30943,7 +30919,7 @@
       <c r="U96" s="49"/>
       <c r="X96"/>
     </row>
-    <row r="97" spans="1:27" ht="14.5" hidden="1">
+    <row r="97" spans="1:27" hidden="1">
       <c r="A97" t="s">
         <v>450</v>
       </c>
@@ -30979,7 +30955,7 @@
       <c r="U97" s="49"/>
       <c r="X97"/>
     </row>
-    <row r="98" spans="1:27" ht="14.5" hidden="1">
+    <row r="98" spans="1:27" hidden="1">
       <c r="A98" t="s">
         <v>453</v>
       </c>
@@ -31012,7 +30988,7 @@
       <c r="U98" s="49"/>
       <c r="X98"/>
     </row>
-    <row r="99" spans="1:27" ht="14.5" hidden="1">
+    <row r="99" spans="1:27" hidden="1">
       <c r="A99" t="s">
         <v>456</v>
       </c>
@@ -31060,7 +31036,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="14.5" hidden="1">
+    <row r="100" spans="1:27" hidden="1">
       <c r="A100" t="s">
         <v>458</v>
       </c>
@@ -31095,7 +31071,7 @@
       </c>
       <c r="U100" s="49"/>
     </row>
-    <row r="101" spans="1:27" ht="14.5" hidden="1">
+    <row r="101" spans="1:27" hidden="1">
       <c r="A101" t="s">
         <v>465</v>
       </c>
@@ -31129,7 +31105,7 @@
       <c r="P101" s="11"/>
       <c r="U101" s="49"/>
     </row>
-    <row r="102" spans="1:27" ht="14.5" hidden="1">
+    <row r="102" spans="1:27" hidden="1">
       <c r="A102" t="s">
         <v>462</v>
       </c>
@@ -31161,7 +31137,7 @@
       <c r="P102" s="11"/>
       <c r="U102" s="49"/>
     </row>
-    <row r="103" spans="1:27" ht="14.5" hidden="1">
+    <row r="103" spans="1:27" hidden="1">
       <c r="A103" t="s">
         <v>460</v>
       </c>
@@ -31193,7 +31169,7 @@
       <c r="P103" s="11"/>
       <c r="U103" s="49"/>
     </row>
-    <row r="104" spans="1:27" ht="14.5">
+    <row r="104" spans="1:27">
       <c r="A104" t="s">
         <v>443</v>
       </c>
@@ -31232,8 +31208,8 @@
       <c r="P104" s="11"/>
       <c r="U104" s="49"/>
     </row>
-    <row r="105" spans="1:27" ht="14.5">
-      <c r="A105" s="147" t="s">
+    <row r="105" spans="1:27">
+      <c r="A105" t="s">
         <v>476</v>
       </c>
       <c r="B105" s="53" t="str">
@@ -31267,8 +31243,8 @@
       <c r="P105" s="11"/>
       <c r="U105" s="49"/>
     </row>
-    <row r="106" spans="1:27" ht="14.5">
-      <c r="A106" s="149" t="s">
+    <row r="106" spans="1:27">
+      <c r="A106" s="33" t="s">
         <v>392</v>
       </c>
       <c r="B106" s="53" t="str">
@@ -31300,7 +31276,7 @@
       <c r="P106" s="11"/>
       <c r="U106" s="49"/>
     </row>
-    <row r="107" spans="1:27" ht="14.5" hidden="1">
+    <row r="107" spans="1:27" hidden="1">
       <c r="A107" t="s">
         <v>467</v>
       </c>
@@ -31342,7 +31318,7 @@
       <c r="P107" s="11"/>
       <c r="U107" s="49"/>
     </row>
-    <row r="108" spans="1:27" ht="14.5" hidden="1">
+    <row r="108" spans="1:27" hidden="1">
       <c r="A108" t="s">
         <v>478</v>
       </c>
@@ -31373,7 +31349,7 @@
       <c r="O108" s="11"/>
       <c r="P108" s="11"/>
     </row>
-    <row r="109" spans="1:27" ht="14.5" hidden="1">
+    <row r="109" spans="1:27" hidden="1">
       <c r="A109" s="136" t="s">
         <v>483</v>
       </c>
@@ -31404,7 +31380,7 @@
       <c r="O109" s="11"/>
       <c r="P109" s="11"/>
     </row>
-    <row r="110" spans="1:27" ht="14.5" hidden="1">
+    <row r="110" spans="1:27" hidden="1">
       <c r="A110" s="136" t="s">
         <v>484</v>
       </c>
@@ -31435,7 +31411,7 @@
       <c r="O110" s="11"/>
       <c r="P110" s="11"/>
     </row>
-    <row r="111" spans="1:27" ht="14.5" hidden="1">
+    <row r="111" spans="1:27" hidden="1">
       <c r="A111" s="136" t="s">
         <v>487</v>
       </c>
@@ -31466,7 +31442,7 @@
       <c r="O111" s="11"/>
       <c r="P111" s="11"/>
     </row>
-    <row r="112" spans="1:27" ht="14.5" hidden="1">
+    <row r="112" spans="1:27" hidden="1">
       <c r="A112" s="136" t="s">
         <v>489</v>
       </c>
@@ -31497,7 +31473,7 @@
       <c r="O112" s="11"/>
       <c r="P112" s="11"/>
     </row>
-    <row r="113" spans="1:16" ht="14.5" hidden="1">
+    <row r="113" spans="1:16" hidden="1">
       <c r="A113" s="136" t="s">
         <v>490</v>
       </c>
@@ -31528,7 +31504,7 @@
       <c r="O113" s="11"/>
       <c r="P113" s="11"/>
     </row>
-    <row r="114" spans="1:16" ht="14.5" hidden="1">
+    <row r="114" spans="1:16" hidden="1">
       <c r="A114" t="s">
         <v>492</v>
       </c>
@@ -31567,8 +31543,8 @@
       <c r="O114" s="11"/>
       <c r="P114" s="11"/>
     </row>
-    <row r="115" spans="1:16" ht="14.5">
-      <c r="A115" s="147" t="s">
+    <row r="115" spans="1:16">
+      <c r="A115" t="s">
         <v>493</v>
       </c>
       <c r="B115" s="53" t="str">
@@ -31601,7 +31577,7 @@
       <c r="O115" s="11"/>
       <c r="P115" s="11"/>
     </row>
-    <row r="116" spans="1:16" ht="14.5" hidden="1">
+    <row r="116" spans="1:16" hidden="1">
       <c r="A116" s="136" t="s">
         <v>496</v>
       </c>
@@ -31632,7 +31608,7 @@
       <c r="O116" s="11"/>
       <c r="P116" s="11"/>
     </row>
-    <row r="117" spans="1:16" ht="14.5" hidden="1">
+    <row r="117" spans="1:16" hidden="1">
       <c r="A117" s="136" t="s">
         <v>498</v>
       </c>
@@ -31663,7 +31639,7 @@
       <c r="O117" s="11"/>
       <c r="P117" s="11"/>
     </row>
-    <row r="118" spans="1:16" ht="14.5" hidden="1">
+    <row r="118" spans="1:16" hidden="1">
       <c r="A118" t="s">
         <v>474</v>
       </c>
@@ -31702,8 +31678,8 @@
       <c r="O118" s="11"/>
       <c r="P118" s="11"/>
     </row>
-    <row r="119" spans="1:16" ht="14.5">
-      <c r="A119" s="147" t="s">
+    <row r="119" spans="1:16">
+      <c r="A119" t="s">
         <v>794</v>
       </c>
       <c r="B119" s="53" t="str">
@@ -31738,7 +31714,7 @@
       <c r="O119" s="11"/>
       <c r="P119" s="11"/>
     </row>
-    <row r="120" spans="1:16" ht="14.5" hidden="1">
+    <row r="120" spans="1:16" hidden="1">
       <c r="A120" s="136" t="s">
         <v>499</v>
       </c>
@@ -31771,41 +31747,41 @@
       <c r="O120" s="11"/>
       <c r="P120" s="11"/>
     </row>
-    <row r="121" spans="1:16" ht="14.5">
+    <row r="121" spans="1:16">
       <c r="M121" s="11"/>
       <c r="N121" s="11"/>
       <c r="O121" s="11"/>
       <c r="P121" s="11"/>
     </row>
-    <row r="122" spans="1:16" ht="14.5">
+    <row r="122" spans="1:16">
       <c r="M122" s="11"/>
       <c r="N122" s="11"/>
       <c r="O122" s="11"/>
       <c r="P122" s="11"/>
     </row>
-    <row r="123" spans="1:16" ht="14.5">
+    <row r="123" spans="1:16">
       <c r="M123" s="11"/>
       <c r="N123" s="11"/>
       <c r="O123" s="11"/>
       <c r="P123" s="11"/>
     </row>
-    <row r="124" spans="1:16" ht="14.5">
+    <row r="124" spans="1:16">
       <c r="O124" s="11"/>
       <c r="P124" s="11"/>
     </row>
-    <row r="125" spans="1:16" ht="14.5">
+    <row r="125" spans="1:16">
       <c r="O125" s="11"/>
       <c r="P125" s="11"/>
     </row>
-    <row r="126" spans="1:16" ht="14.5">
+    <row r="126" spans="1:16">
       <c r="O126" s="11"/>
       <c r="P126" s="11"/>
     </row>
-    <row r="127" spans="1:16" ht="14.5">
+    <row r="127" spans="1:16">
       <c r="O127" s="11"/>
       <c r="P127" s="11"/>
     </row>
-    <row r="128" spans="1:16" ht="14.5">
+    <row r="128" spans="1:16">
       <c r="O128" s="11"/>
       <c r="P128" s="11"/>
     </row>
@@ -31873,23 +31849,23 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:Y136"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16.453125" style="73" customWidth="1"/>
-    <col min="2" max="3" width="16.81640625" style="73" customWidth="1"/>
-    <col min="4" max="4" width="24.1796875" style="73" customWidth="1"/>
-    <col min="5" max="5" width="21.54296875" style="73" customWidth="1"/>
-    <col min="6" max="6" width="42.54296875" style="73" customWidth="1"/>
+    <col min="1" max="1" width="16.5" style="73" customWidth="1"/>
+    <col min="2" max="3" width="16.83203125" style="73" customWidth="1"/>
+    <col min="4" max="4" width="24.1640625" style="73" customWidth="1"/>
+    <col min="5" max="5" width="21.5" style="73" customWidth="1"/>
+    <col min="6" max="6" width="42.5" style="73" customWidth="1"/>
     <col min="7" max="7" width="14" style="73" customWidth="1"/>
-    <col min="8" max="8" width="24.81640625" style="99" customWidth="1"/>
-    <col min="9" max="9" width="10.81640625" style="73" customWidth="1"/>
-    <col min="10" max="12" width="12.54296875" style="73" customWidth="1"/>
-    <col min="13" max="24" width="9.81640625" style="73" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.54296875" style="73" customWidth="1"/>
-    <col min="26" max="16384" width="9.1796875" style="73"/>
+    <col min="8" max="8" width="24.83203125" style="99" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" style="73" customWidth="1"/>
+    <col min="10" max="12" width="12.5" style="73" customWidth="1"/>
+    <col min="13" max="24" width="9.83203125" style="73" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.5" style="73" customWidth="1"/>
+    <col min="26" max="16384" width="9.1640625" style="73"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" ht="15">
       <c r="A1" s="69" t="s">
         <v>629</v>
       </c>
@@ -31926,27 +31902,27 @@
       <c r="L1" s="70" t="s">
         <v>629</v>
       </c>
-      <c r="M1" s="145" t="s">
+      <c r="M1" s="146" t="s">
         <v>631</v>
       </c>
-      <c r="N1" s="145"/>
-      <c r="O1" s="145"/>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="145"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145" t="s">
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="146"/>
+      <c r="S1" s="146" t="s">
         <v>631</v>
       </c>
-      <c r="T1" s="146"/>
-      <c r="U1" s="146"/>
-      <c r="V1" s="146"/>
-      <c r="W1" s="146"/>
-      <c r="X1" s="146"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="147"/>
+      <c r="X1" s="147"/>
       <c r="Y1" s="72" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" ht="15">
       <c r="A2" s="74" t="s">
         <v>632</v>
       </c>
@@ -32023,7 +31999,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="3" spans="1:25" customFormat="1" ht="14.5">
+    <row r="3" spans="1:25" customFormat="1" ht="15">
       <c r="A3" s="18" t="str">
         <f>IF(F3=""," ",VLOOKUP(F3,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -32083,7 +32059,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="4" spans="1:25" customFormat="1" ht="14.5">
+    <row r="4" spans="1:25" customFormat="1" ht="15">
       <c r="A4" s="18" t="str">
         <f>IF(F4=""," ",VLOOKUP(F4,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -32164,7 +32140,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="5" spans="1:25" customFormat="1" ht="14.5">
+    <row r="5" spans="1:25" customFormat="1" ht="15">
       <c r="A5" s="18" t="str">
         <f>IF(F5=""," ",VLOOKUP(F5,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -32222,7 +32198,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="6" spans="1:25" customFormat="1" ht="14.5">
+    <row r="6" spans="1:25" customFormat="1" ht="15">
       <c r="A6" s="18" t="str">
         <f>IF(F6=""," ",VLOOKUP(F6,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -32282,7 +32258,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="7" spans="1:25" customFormat="1" ht="14.5">
+    <row r="7" spans="1:25" customFormat="1" ht="15">
       <c r="A7" s="18" t="str">
         <f>IF(F7=""," ",VLOOKUP(F7,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -32363,7 +32339,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="8" spans="1:25" customFormat="1" ht="14.5">
+    <row r="8" spans="1:25" customFormat="1" ht="15">
       <c r="A8" s="18" t="str">
         <f>IF(F8=""," ",VLOOKUP(F8,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -32447,7 +32423,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="9" spans="1:25" customFormat="1" ht="14.5">
+    <row r="9" spans="1:25" customFormat="1" ht="15">
       <c r="A9" s="18" t="str">
         <f>IF(F9=""," ",VLOOKUP(F9,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -32531,7 +32507,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="10" spans="1:25" customFormat="1" ht="14.5">
+    <row r="10" spans="1:25" customFormat="1" ht="15">
       <c r="A10" s="18" t="str">
         <f>IF(F10=""," ",VLOOKUP(F10,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -32603,7 +32579,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="11" spans="1:25" customFormat="1" ht="14.5">
+    <row r="11" spans="1:25" customFormat="1" ht="15">
       <c r="A11" s="18" t="str">
         <f>IF(F11=""," ",VLOOKUP(F11,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -32684,7 +32660,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="12" spans="1:25" customFormat="1" ht="14.5">
+    <row r="12" spans="1:25" customFormat="1" ht="15">
       <c r="A12" s="18" t="str">
         <f>IF(F12=""," ",VLOOKUP(F12,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -32741,7 +32717,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="13" spans="1:25" customFormat="1" ht="14.5">
+    <row r="13" spans="1:25" customFormat="1" ht="15">
       <c r="A13" s="18" t="str">
         <f>IF(F13=""," ",VLOOKUP(F13,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -32825,7 +32801,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="14" spans="1:25" customFormat="1" ht="14.5">
+    <row r="14" spans="1:25" customFormat="1" ht="15">
       <c r="A14" s="18" t="str">
         <f>IF(F14=""," ",VLOOKUP(F14,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -32909,7 +32885,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" ht="15">
       <c r="A15" s="18" t="str">
         <f>IF(F15=""," ",VLOOKUP(F15,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -32994,7 +32970,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" ht="15">
       <c r="A16" s="18" t="str">
         <f>IF(F16=""," ",VLOOKUP(F16,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -33079,7 +33055,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" ht="15">
       <c r="A17" s="18" t="str">
         <f>IF(F17=""," ",VLOOKUP(F17,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -33146,7 +33122,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" ht="15">
       <c r="A18" s="18" t="str">
         <f>IF(F18=""," ",VLOOKUP(F18,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -33224,7 +33200,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" ht="15">
       <c r="A19" s="18" t="str">
         <f>IF(F19=""," ",VLOOKUP(F19,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -33292,7 +33268,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" ht="15">
       <c r="A20" s="18" t="str">
         <f>IF(F20=""," ",VLOOKUP(F20,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -33364,7 +33340,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" ht="15">
       <c r="A21" s="18" t="str">
         <f>IF(F21=""," ",VLOOKUP(F21,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -33428,7 +33404,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="22" spans="1:25" customFormat="1">
+    <row r="22" spans="1:25" customFormat="1" ht="15">
       <c r="A22" s="18" t="str">
         <f>IF(F22=""," ",VLOOKUP(F22,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -33492,7 +33468,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="23" spans="1:25" customFormat="1">
+    <row r="23" spans="1:25" customFormat="1" ht="15">
       <c r="A23" s="18" t="str">
         <f>IF(F23=""," ",VLOOKUP(F23,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -33577,7 +33553,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="24" spans="1:25" customFormat="1">
+    <row r="24" spans="1:25" customFormat="1" ht="15">
       <c r="A24" s="18" t="str">
         <f>IF(F24=""," ",VLOOKUP(F24,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -33662,7 +33638,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="25" spans="1:25" customFormat="1">
+    <row r="25" spans="1:25" customFormat="1" ht="15">
       <c r="A25" s="18" t="str">
         <f>IF(F25=""," ",VLOOKUP(F25,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -33733,7 +33709,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="26" spans="1:25" customFormat="1">
+    <row r="26" spans="1:25" customFormat="1" ht="15">
       <c r="A26" s="18" t="str">
         <f>IF(F26=""," ",VLOOKUP(F26,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -33815,7 +33791,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" ht="15">
       <c r="A27" s="18" t="str">
         <f>IF(F27=""," ",VLOOKUP(F27,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -33896,7 +33872,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" ht="15">
       <c r="A28" s="18" t="str">
         <f>IF(F28=""," ",VLOOKUP(F28,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -33980,7 +33956,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="29" spans="1:25" customFormat="1">
+    <row r="29" spans="1:25" customFormat="1" ht="15">
       <c r="A29" s="18" t="str">
         <f>IF(F29=""," ",VLOOKUP(F29,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -34065,7 +34041,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" ht="15">
       <c r="A30" s="18" t="str">
         <f>IF(F30=""," ",VLOOKUP(F30,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -34131,7 +34107,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" ht="15">
       <c r="A31" s="18" t="str">
         <f>IF(F31=""," ",VLOOKUP(F31,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -34185,7 +34161,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="32" spans="1:25" customFormat="1">
+    <row r="32" spans="1:25" customFormat="1" ht="15">
       <c r="A32" s="18" t="str">
         <f>IF(F32=""," ",VLOOKUP(F32,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -34249,7 +34225,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="33" spans="1:25" customFormat="1">
+    <row r="33" spans="1:25" customFormat="1" ht="15">
       <c r="A33" s="18" t="str">
         <f>IF(F33=""," ",VLOOKUP(F33,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -34334,7 +34310,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="34" spans="1:25" customFormat="1" ht="14.5">
+    <row r="34" spans="1:25" customFormat="1" ht="15">
       <c r="A34" s="18" t="str">
         <f>IF(F34=""," ",VLOOKUP(F34,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -34418,7 +34394,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="35" spans="1:25" customFormat="1" ht="14.5">
+    <row r="35" spans="1:25" customFormat="1" ht="15">
       <c r="A35" s="18" t="str">
         <f>IF(F35=""," ",VLOOKUP(F35,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -34484,7 +34460,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="36" spans="1:25" customFormat="1" ht="14.5">
+    <row r="36" spans="1:25" customFormat="1" ht="15">
       <c r="A36" s="18" t="str">
         <f>IF(F36=""," ",VLOOKUP(F36,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -34546,7 +34522,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" ht="15">
       <c r="A37" s="18" t="str">
         <f>IF(F37=""," ",VLOOKUP(F37,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -34631,7 +34607,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" ht="15">
       <c r="A38" s="18" t="str">
         <f>IF(F38=""," ",VLOOKUP(F38,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -34710,7 +34686,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="39" spans="1:25" customFormat="1">
+    <row r="39" spans="1:25" customFormat="1" ht="15">
       <c r="A39" s="18" t="str">
         <f>IF(F39=""," ",VLOOKUP(F39,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -34783,7 +34759,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="40" spans="1:25" customFormat="1">
+    <row r="40" spans="1:25" customFormat="1" ht="15">
       <c r="A40" s="18" t="str">
         <f>IF(F40=""," ",VLOOKUP(F40,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -34868,7 +34844,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" ht="15">
       <c r="A41" s="18" t="str">
         <f>IF(F41=""," ",VLOOKUP(F41,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -34928,7 +34904,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="42" spans="1:25" customFormat="1" ht="14.5">
+    <row r="42" spans="1:25" customFormat="1" ht="15">
       <c r="A42" s="18" t="str">
         <f>IF(F42=""," ",VLOOKUP(F42,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -35012,7 +34988,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="43" spans="1:25" customFormat="1">
+    <row r="43" spans="1:25" customFormat="1" ht="15">
       <c r="A43" s="18" t="str">
         <f>IF(F43=""," ",VLOOKUP(F43,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -35097,7 +35073,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="44" spans="1:25" customFormat="1">
+    <row r="44" spans="1:25" customFormat="1" ht="15">
       <c r="A44" s="18" t="str">
         <f>IF(F44=""," ",VLOOKUP(F44,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -35182,7 +35158,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="45" spans="1:25" customFormat="1" ht="14.5">
+    <row r="45" spans="1:25" customFormat="1" ht="15">
       <c r="A45" s="18" t="str">
         <f>IF(F45=""," ",VLOOKUP(F45,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -35233,7 +35209,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="46" spans="1:25" customFormat="1" ht="14.5">
+    <row r="46" spans="1:25" customFormat="1" ht="15">
       <c r="A46" s="18" t="str">
         <f>IF(F46=""," ",VLOOKUP(F46,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -35298,7 +35274,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="47" spans="1:25" customFormat="1" ht="14.5">
+    <row r="47" spans="1:25" customFormat="1" ht="15">
       <c r="A47" s="18" t="str">
         <f>IF(F47=""," ",VLOOKUP(F47,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -35379,7 +35355,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" ht="15">
       <c r="A48" s="18" t="str">
         <f>IF(F48=""," ",VLOOKUP(F48,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -35462,7 +35438,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="49" spans="1:25" customFormat="1">
+    <row r="49" spans="1:25" customFormat="1" ht="15">
       <c r="A49" s="18" t="str">
         <f>IF(F49=""," ",VLOOKUP(F49,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -35545,7 +35521,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="50" spans="1:25" customFormat="1">
+    <row r="50" spans="1:25" customFormat="1" ht="15">
       <c r="A50" s="18" t="str">
         <f>IF(F50=""," ",VLOOKUP(F50,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -35626,7 +35602,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="51" spans="1:25" customFormat="1">
+    <row r="51" spans="1:25" customFormat="1" ht="15">
       <c r="A51" s="18" t="str">
         <f>IF(F51=""," ",VLOOKUP(F51,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -35693,7 +35669,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="52" spans="1:25" customFormat="1" ht="14.5">
+    <row r="52" spans="1:25" customFormat="1" ht="15">
       <c r="A52" s="18" t="str">
         <f>IF(F52=""," ",VLOOKUP(F52,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -35777,7 +35753,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="53" spans="1:25" customFormat="1" ht="14.5">
+    <row r="53" spans="1:25" customFormat="1" ht="15">
       <c r="A53" s="18" t="str">
         <f>IF(F53=""," ",VLOOKUP(F53,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -35843,7 +35819,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="54" spans="1:25" customFormat="1">
+    <row r="54" spans="1:25" customFormat="1" ht="15">
       <c r="A54" s="18" t="str">
         <f>IF(F54=""," ",VLOOKUP(F54,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -35928,7 +35904,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="55" spans="1:25" customFormat="1">
+    <row r="55" spans="1:25" customFormat="1" ht="15">
       <c r="A55" s="18" t="str">
         <f>IF(F55=""," ",VLOOKUP(F55,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -36009,7 +35985,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="56" spans="1:25" customFormat="1">
+    <row r="56" spans="1:25" customFormat="1" ht="15">
       <c r="A56" s="18" t="str">
         <f>IF(F56=""," ",VLOOKUP(F56,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -36092,7 +36068,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="57" spans="1:25" customFormat="1" ht="14.5">
+    <row r="57" spans="1:25" customFormat="1" ht="15">
       <c r="A57" s="18" t="str">
         <f>IF(F57=""," ",VLOOKUP(F57,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -36157,7 +36133,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="58" spans="1:25" customFormat="1" ht="14.5">
+    <row r="58" spans="1:25" customFormat="1" ht="15">
       <c r="A58" s="18" t="str">
         <f>IF(F58=""," ",VLOOKUP(F58,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -36241,7 +36217,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="59" spans="1:25" customFormat="1" ht="14.5">
+    <row r="59" spans="1:25" customFormat="1" ht="15">
       <c r="A59" s="18" t="str">
         <f>IF(F59=""," ",VLOOKUP(F59,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -36307,7 +36283,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="60" spans="1:25" customFormat="1" ht="14.5">
+    <row r="60" spans="1:25" customFormat="1" ht="15">
       <c r="A60" s="18" t="str">
         <f>IF(F60=""," ",VLOOKUP(F60,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -36375,7 +36351,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="61" spans="1:25" customFormat="1">
+    <row r="61" spans="1:25" customFormat="1" ht="15">
       <c r="A61" s="18" t="str">
         <f>IF(F61=""," ",VLOOKUP(F61,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -36448,7 +36424,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="62" spans="1:25" customFormat="1" ht="14.5">
+    <row r="62" spans="1:25" customFormat="1" ht="15">
       <c r="A62" s="18" t="str">
         <f>IF(F62=""," ",VLOOKUP(F62,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -36532,7 +36508,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="63" spans="1:25" customFormat="1" ht="14.5">
+    <row r="63" spans="1:25" customFormat="1" ht="15">
       <c r="A63" s="18" t="str">
         <f>IF(F63=""," ",VLOOKUP(F63,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -36614,7 +36590,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="64" spans="1:25" customFormat="1" ht="14.5">
+    <row r="64" spans="1:25" customFormat="1" ht="15">
       <c r="A64" s="18" t="str">
         <f>IF(F64=""," ",VLOOKUP(F64,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -36682,7 +36658,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="65" spans="1:25" customFormat="1">
+    <row r="65" spans="1:25" customFormat="1" ht="15">
       <c r="A65" s="18" t="str">
         <f>IF(F65=""," ",VLOOKUP(F65,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -36757,7 +36733,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" ht="15">
       <c r="A66" s="18" t="str">
         <f>IF(F66=""," ",VLOOKUP(F66,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -36838,7 +36814,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" ht="15">
       <c r="A67" s="18" t="str">
         <f>IF(F67=""," ",VLOOKUP(F67,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -36923,7 +36899,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" ht="15">
       <c r="A68" s="18" t="str">
         <f>IF(F68=""," ",VLOOKUP(F68,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -37061,7 +37037,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="70" spans="1:25" customFormat="1" ht="14.5">
+    <row r="70" spans="1:25" customFormat="1" ht="15">
       <c r="A70" s="18" t="str">
         <f>IF(F70=""," ",VLOOKUP(F70,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -37142,7 +37118,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="71" spans="1:25" customFormat="1" ht="14.5">
+    <row r="71" spans="1:25" customFormat="1" ht="15">
       <c r="A71" s="18" t="str">
         <f>IF(F71=""," ",VLOOKUP(F71,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -37226,7 +37202,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="72" spans="1:25" customFormat="1" ht="14.5">
+    <row r="72" spans="1:25" customFormat="1" ht="15">
       <c r="A72" s="18" t="str">
         <f>IF(F72=""," ",VLOOKUP(F72,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -37298,7 +37274,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="73" spans="1:25" customFormat="1" ht="14.5">
+    <row r="73" spans="1:25" customFormat="1" ht="15">
       <c r="A73" s="18" t="str">
         <f>IF(F73=""," ",VLOOKUP(F73,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -37357,7 +37333,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="74" spans="1:25" customFormat="1" ht="14.5">
+    <row r="74" spans="1:25" customFormat="1" ht="15">
       <c r="A74" s="18" t="str">
         <f>IF(F74=""," ",VLOOKUP(F74,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -37429,7 +37405,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="75" spans="1:25" customFormat="1" ht="14.5">
+    <row r="75" spans="1:25" customFormat="1" ht="15">
       <c r="A75" s="18" t="str">
         <f>IF(F75=""," ",VLOOKUP(F75,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -37507,7 +37483,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="76" spans="1:25" customFormat="1" ht="14.5">
+    <row r="76" spans="1:25" customFormat="1" ht="15">
       <c r="A76" s="18" t="str">
         <f>IF(F76=""," ",VLOOKUP(F76,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -37585,7 +37561,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="77" spans="1:25" customFormat="1" ht="14.5">
+    <row r="77" spans="1:25" customFormat="1" ht="15">
       <c r="A77" s="18" t="str">
         <f>IF(F77=""," ",VLOOKUP(F77,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -37633,7 +37609,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="78" spans="1:25" customFormat="1" ht="14.5">
+    <row r="78" spans="1:25" customFormat="1" ht="15">
       <c r="A78" s="18" t="str">
         <f>IF(F78=""," ",VLOOKUP(F78,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -37701,7 +37677,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="79" spans="1:25" customFormat="1" ht="14.5">
+    <row r="79" spans="1:25" customFormat="1" ht="15">
       <c r="A79" s="18" t="str">
         <f>IF(F79=""," ",VLOOKUP(F79,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -37765,7 +37741,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="80" spans="1:25" customFormat="1" ht="14.5">
+    <row r="80" spans="1:25" customFormat="1" ht="15">
       <c r="A80" s="18" t="str">
         <f>IF(F80=""," ",VLOOKUP(F80,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -37849,7 +37825,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="81" spans="1:25" customFormat="1">
+    <row r="81" spans="1:25" customFormat="1" ht="15">
       <c r="A81" s="18" t="str">
         <f>IF(F81=""," ",VLOOKUP(F81,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -37918,7 +37894,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="82" spans="1:25" customFormat="1">
+    <row r="82" spans="1:25" customFormat="1" ht="15">
       <c r="A82" s="18" t="str">
         <f>IF(F82=""," ",VLOOKUP(F82,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -38003,7 +37979,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="83" spans="1:25" customFormat="1">
+    <row r="83" spans="1:25" customFormat="1" ht="15">
       <c r="A83" s="18" t="str">
         <f>IF(F83=""," ",VLOOKUP(F83,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -38072,7 +38048,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="84" spans="1:25" customFormat="1" ht="14.5">
+    <row r="84" spans="1:25" customFormat="1" ht="15">
       <c r="A84" s="18" t="str">
         <f>IF(F84=""," ",VLOOKUP(F84,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -38138,7 +38114,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="85" spans="1:25" customFormat="1" ht="14.5">
+    <row r="85" spans="1:25" customFormat="1" ht="15">
       <c r="A85" s="18" t="str">
         <f>IF(F85=""," ",VLOOKUP(F85,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -38210,7 +38186,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="86" spans="1:25" customFormat="1" ht="14.5">
+    <row r="86" spans="1:25" customFormat="1" ht="15">
       <c r="A86" s="18" t="str">
         <f>IF(F86=""," ",VLOOKUP(F86,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -38282,7 +38258,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="87" spans="1:25" customFormat="1" ht="14.5">
+    <row r="87" spans="1:25" customFormat="1" ht="15">
       <c r="A87" s="18" t="str">
         <f>IF(F87=""," ",VLOOKUP(F87,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -38360,7 +38336,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="88" spans="1:25" customFormat="1" ht="14.5">
+    <row r="88" spans="1:25" customFormat="1" ht="15">
       <c r="A88" s="18" t="str">
         <f>IF(F88=""," ",VLOOKUP(F88,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -38438,7 +38414,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="89" spans="1:25" customFormat="1" ht="14.5">
+    <row r="89" spans="1:25" customFormat="1" ht="15">
       <c r="A89" s="18" t="str">
         <f>IF(F89=""," ",VLOOKUP(F89,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -38522,7 +38498,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="90" spans="1:25" customFormat="1" ht="14.5">
+    <row r="90" spans="1:25" customFormat="1" ht="15">
       <c r="A90" s="18" t="str">
         <f>IF(F90=""," ",VLOOKUP(F90,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -38596,7 +38572,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="91" spans="1:25" customFormat="1">
+    <row r="91" spans="1:25" customFormat="1" ht="15">
       <c r="A91" s="18" t="str">
         <f>IF(F91=""," ",VLOOKUP(F91,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -38675,7 +38651,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="92" spans="1:25" customFormat="1">
+    <row r="92" spans="1:25" customFormat="1" ht="15">
       <c r="A92" s="18" t="str">
         <f>IF(F92=""," ",VLOOKUP(F92,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -38757,7 +38733,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="93" spans="1:25" customFormat="1">
+    <row r="93" spans="1:25" customFormat="1" ht="15">
       <c r="A93" s="18" t="str">
         <f>IF(F93=""," ",VLOOKUP(F93,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -38822,7 +38798,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="94" spans="1:25" customFormat="1">
+    <row r="94" spans="1:25" customFormat="1" ht="15">
       <c r="A94" s="18" t="str">
         <f>IF(F94=""," ",VLOOKUP(F94,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -38886,7 +38862,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="95" spans="1:25" customFormat="1">
+    <row r="95" spans="1:25" customFormat="1" ht="15">
       <c r="A95" s="18" t="str">
         <f>IF(F95=""," ",VLOOKUP(F95,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -38950,7 +38926,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="96" spans="1:25" customFormat="1">
+    <row r="96" spans="1:25" customFormat="1" ht="15">
       <c r="A96" s="18" t="str">
         <f>IF(F96=""," ",VLOOKUP(F96,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -39014,7 +38990,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="97" spans="1:25" customFormat="1">
+    <row r="97" spans="1:25" customFormat="1" ht="15">
       <c r="A97" s="18" t="str">
         <f>IF(F97=""," ",VLOOKUP(F97,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -39075,7 +39051,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="98" spans="1:25" customFormat="1">
+    <row r="98" spans="1:25" customFormat="1" ht="15">
       <c r="A98" s="18" t="str">
         <f>IF(F98=""," ",VLOOKUP(F98,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -39150,7 +39126,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="99" spans="1:25" customFormat="1">
+    <row r="99" spans="1:25" customFormat="1" ht="15">
       <c r="A99" s="18" t="str">
         <f>IF(F99=""," ",VLOOKUP(F99,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -39215,7 +39191,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="100" spans="1:25" customFormat="1">
+    <row r="100" spans="1:25" customFormat="1" ht="15">
       <c r="A100" s="18" t="str">
         <f>IF(F100=""," ",VLOOKUP(F100,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -39290,7 +39266,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="101" spans="1:25" customFormat="1" ht="14.5">
+    <row r="101" spans="1:25" customFormat="1" ht="15">
       <c r="A101" s="18" t="str">
         <f>IF(F101=""," ",VLOOKUP(F101,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -39363,7 +39339,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="102" spans="1:25" customFormat="1" ht="14.5">
+    <row r="102" spans="1:25" customFormat="1" ht="15">
       <c r="A102" s="18" t="str">
         <f>IF(F102=""," ",VLOOKUP(F102,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -39428,7 +39404,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="103" spans="1:25" customFormat="1" ht="14.5">
+    <row r="103" spans="1:25" customFormat="1" ht="15">
       <c r="A103" s="18" t="str">
         <f>IF(F103=""," ",VLOOKUP(F103,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -39494,7 +39470,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="104" spans="1:25" customFormat="1" ht="14.5">
+    <row r="104" spans="1:25" customFormat="1" ht="15">
       <c r="A104" s="18" t="str">
         <f>IF(F104=""," ",VLOOKUP(F104,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -39561,7 +39537,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" ht="15">
       <c r="A105" s="18" t="str">
         <f>IF(F105=""," ",VLOOKUP(F105,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -39625,7 +39601,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" ht="15">
       <c r="A106" s="18" t="str">
         <f>IF(F106=""," ",VLOOKUP(F106,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -39691,7 +39667,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" ht="15">
       <c r="A107" s="18" t="str">
         <f>IF(F107=""," ",VLOOKUP(F107,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -39747,7 +39723,7 @@
       <c r="W107" s="116"/>
       <c r="X107" s="116"/>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" ht="15">
       <c r="A108" s="18" t="str">
         <f>IF(F108=""," ",VLOOKUP(F108,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -39813,7 +39789,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" ht="15">
       <c r="A109" s="18" t="str">
         <f>IF(F109=""," ",VLOOKUP(F109,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -39871,7 +39847,7 @@
       <c r="W109" s="116"/>
       <c r="X109" s="116"/>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" ht="15">
       <c r="A110" s="18" t="str">
         <f>IF(F110=""," ",VLOOKUP(F110,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -39927,7 +39903,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" ht="15">
       <c r="A111" s="18" t="e">
         <f>IF(F111=""," ",VLOOKUP(F111,'Project List 2026'!A:J,3,0))</f>
         <v>#N/A</v>
@@ -39971,7 +39947,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" ht="15">
       <c r="A112" s="18" t="e">
         <f>IF(F112=""," ",VLOOKUP(F112,'Project List 2026'!A:J,3,0))</f>
         <v>#N/A</v>
@@ -40015,7 +39991,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="113" spans="1:24">
+    <row r="113" spans="1:24" ht="15">
       <c r="A113" s="18" t="e">
         <f>IF(F113=""," ",VLOOKUP(F113,'Project List 2026'!A:J,3,0))</f>
         <v>#N/A</v>
@@ -40059,7 +40035,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="114" spans="1:24">
+    <row r="114" spans="1:24" ht="15">
       <c r="A114" s="18" t="e">
         <f>IF(F114=""," ",VLOOKUP(F114,'Project List 2026'!A:J,3,0))</f>
         <v>#N/A</v>
@@ -40103,7 +40079,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="115" spans="1:24">
+    <row r="115" spans="1:24" ht="15">
       <c r="A115" s="18" t="e">
         <f>IF(F115=""," ",VLOOKUP(F115,'Project List 2026'!A:J,3,0))</f>
         <v>#N/A</v>
@@ -40147,7 +40123,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="116" spans="1:24">
+    <row r="116" spans="1:24" ht="15">
       <c r="A116" s="18" t="str">
         <f>IF(F116=""," ",VLOOKUP(F116,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -40206,7 +40182,7 @@
       <c r="W116" s="1"/>
       <c r="X116" s="1"/>
     </row>
-    <row r="117" spans="1:24">
+    <row r="117" spans="1:24" ht="15">
       <c r="A117" s="18" t="str">
         <f>IF(F117=""," ",VLOOKUP(F117,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -40265,7 +40241,7 @@
       <c r="W117" s="1"/>
       <c r="X117" s="1"/>
     </row>
-    <row r="118" spans="1:24">
+    <row r="118" spans="1:24" ht="15">
       <c r="A118" s="18" t="str">
         <f>IF(F118=""," ",VLOOKUP(F118,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -40316,7 +40292,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="119" spans="1:24">
+    <row r="119" spans="1:24" ht="15">
       <c r="A119" s="18" t="str">
         <f>IF(F119=""," ",VLOOKUP(F119,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -40367,7 +40343,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="120" spans="1:24">
+    <row r="120" spans="1:24" ht="15">
       <c r="A120" s="18" t="e">
         <f>IF(F120=""," ",VLOOKUP(F120,'Project List 2026'!A:J,3,0))</f>
         <v>#N/A</v>
@@ -40424,7 +40400,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="121" spans="1:24">
+    <row r="121" spans="1:24" ht="15">
       <c r="A121" s="18" t="str">
         <f>IF(F121=""," ",VLOOKUP(F121,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -40481,7 +40457,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="122" spans="1:24">
+    <row r="122" spans="1:24" ht="15">
       <c r="A122" s="18" t="str">
         <f>IF(F122=""," ",VLOOKUP(F122,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -40538,7 +40514,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="123" spans="1:24">
+    <row r="123" spans="1:24" ht="15">
       <c r="A123" s="18" t="str">
         <f>IF(F123=""," ",VLOOKUP(F123,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -40595,7 +40571,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="124" spans="1:24">
+    <row r="124" spans="1:24" ht="15">
       <c r="A124" s="18" t="str">
         <f>IF(F124=""," ",VLOOKUP(F124,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -40658,7 +40634,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="125" spans="1:24">
+    <row r="125" spans="1:24" ht="15">
       <c r="A125" s="18" t="str">
         <f>IF(F125=""," ",VLOOKUP(F125,'Project List 2026'!A:J,3,0))</f>
         <v>APAC</v>
@@ -40718,7 +40694,7 @@
       <c r="W125" s="116"/>
       <c r="X125" s="116"/>
     </row>
-    <row r="126" spans="1:24">
+    <row r="126" spans="1:24" ht="15">
       <c r="A126" s="18" t="e">
         <f>IF(F126=""," ",VLOOKUP(F126,'Project List 2026'!A:J,3,0))</f>
         <v>#N/A</v>
@@ -40772,7 +40748,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="127" spans="1:24">
+    <row r="127" spans="1:24" ht="15">
       <c r="A127" s="18" t="e">
         <f>IF(F127=""," ",VLOOKUP(F127,'Project List 2026'!A:J,3,0))</f>
         <v>#N/A</v>
@@ -40827,7 +40803,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="128" spans="1:24">
+    <row r="128" spans="1:24" ht="15">
       <c r="A128" s="18" t="str">
         <f>IF(F128=""," ",VLOOKUP(F128,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -40878,7 +40854,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="129" spans="1:24">
+    <row r="129" spans="1:24" ht="15">
       <c r="A129" s="18" t="str">
         <f>IF(F129=""," ",VLOOKUP(F129,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -40941,7 +40917,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="130" spans="1:24">
+    <row r="130" spans="1:24" ht="15">
       <c r="A130" s="18" t="str">
         <f>IF(F130=""," ",VLOOKUP(F130,'Project List 2026'!A:J,3,0))</f>
         <v>Telecoms</v>
@@ -41004,7 +40980,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="131" spans="1:24">
+    <row r="131" spans="1:24" ht="15">
       <c r="A131" s="18" t="str">
         <f>IF(F131=""," ",VLOOKUP(F131,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -41047,7 +41023,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="132" spans="1:24">
+    <row r="132" spans="1:24" ht="15">
       <c r="A132" s="18" t="e">
         <f>IF(F132=""," ",VLOOKUP(F132,'Project List 2026'!A:J,3,0))</f>
         <v>#N/A</v>
@@ -41099,7 +41075,7 @@
       </c>
       <c r="U132" s="82"/>
     </row>
-    <row r="133" spans="1:24">
+    <row r="133" spans="1:24" ht="15">
       <c r="A133" s="18" t="str">
         <f>IF(F133=""," ",VLOOKUP(F133,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -41146,7 +41122,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="134" spans="1:24">
+    <row r="134" spans="1:24" ht="15">
       <c r="A134" s="18" t="str">
         <f>IF(F134=""," ",VLOOKUP(F134,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -41193,7 +41169,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="135" spans="1:24">
+    <row r="135" spans="1:24" ht="15">
       <c r="A135" s="18" t="str">
         <f>IF(F135=""," ",VLOOKUP(F135,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -41241,7 +41217,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="136" spans="1:24">
+    <row r="136" spans="1:24" ht="15">
       <c r="A136" s="18" t="str">
         <f>IF(F136=""," ",VLOOKUP(F136,'Project List 2026'!A:J,3,0))</f>
         <v>Hosting</v>
@@ -41303,15 +41279,15 @@
     <tabColor theme="0" tint="-0.14999847407452621"/>
   </sheetPr>
   <dimension ref="A1:M20"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="13" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="1.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="13" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="1.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -41904,54 +41880,54 @@
     </row>
   </sheetData>
   <conditionalFormatting pivot="1" sqref="B8:M19">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="189" priority="10" operator="greaterThan">
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="B8:M19">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="188" priority="9" operator="between">
       <formula>0.5</formula>
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="B8:M19">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="187" priority="8" operator="lessThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="B8:M19">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="186" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="B8:M19">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="185" priority="6" operator="greaterThan">
       <formula>75</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="B8:M19">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="184" priority="5" operator="greaterThan">
       <formula>0.75</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="B8:M19">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="183" priority="4" operator="between">
       <formula>0.45</formula>
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="B8:M19">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="182" priority="3" operator="lessThan">
       <formula>0.45</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="B8:M19">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="181" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="B8:M19">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="180" priority="1" operator="between">
       <formula>0.45</formula>
       <formula>0.75</formula>
     </cfRule>
@@ -41963,29 +41939,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7374901E-41D3-4DFF-A0DA-9281F29711A8}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="35" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="17" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
@@ -43126,46 +43102,46 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B4D1359-997A-4B32-9D61-32137B644E20}">
   <dimension ref="A4:B46"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="16" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.5" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="11" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="1:2">
@@ -43356,20 +43332,20 @@
     <tabColor theme="1" tint="0.14999847407452621"/>
   </sheetPr>
   <dimension ref="B2:AH67"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
     <col min="8" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="11.1796875" customWidth="1"/>
+    <col min="15" max="15" width="11.1640625" customWidth="1"/>
     <col min="16" max="28" width="0" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="1.81640625" customWidth="1"/>
-    <col min="32" max="32" width="15.54296875" customWidth="1"/>
+    <col min="29" max="29" width="1.83203125" customWidth="1"/>
+    <col min="32" max="32" width="15.5" customWidth="1"/>
     <col min="33" max="33" width="19" customWidth="1"/>
-    <col min="34" max="34" width="28.54296875" customWidth="1"/>
+    <col min="34" max="34" width="28.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:34" ht="58">
+    <row r="2" spans="2:34" ht="64">
       <c r="B2" s="28" t="s">
         <v>509</v>
       </c>
@@ -44293,12 +44269,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -44479,15 +44452,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7280A60D-F491-40BE-A66A-3984376BAB35}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C88CD8BE-31D6-4BB5-AA1E-0319A97B8FD9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cb9b8e19-05c6-45d6-a269-b3ac1248d174"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="0cf4979e-db03-4f4a-a57c-d8af81fe2f2a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -44512,18 +44497,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C88CD8BE-31D6-4BB5-AA1E-0319A97B8FD9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7280A60D-F491-40BE-A66A-3984376BAB35}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="cb9b8e19-05c6-45d6-a269-b3ac1248d174"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="0cf4979e-db03-4f4a-a57c-d8af81fe2f2a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
